--- a/scalping-bot/reports/backtest_report.xlsx
+++ b/scalping-bot/reports/backtest_report.xlsx
@@ -490,37 +490,37 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>M15</t>
+          <t>H1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2020-06-01 -&gt; 2022-03-04</t>
+          <t>2024-06-06 -&gt; 2025-06-06</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>32</v>
+        <v>144</v>
       </c>
       <c r="E2" t="n">
-        <v>25</v>
+        <v>39.6</v>
       </c>
       <c r="F2" t="n">
-        <v>-547.91</v>
+        <v>-320.07</v>
       </c>
       <c r="G2" t="n">
-        <v>-47.91</v>
+        <v>179.93</v>
       </c>
       <c r="H2" t="n">
-        <v>106.9</v>
+        <v>71.09999999999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.49</v>
+        <v>0.63</v>
       </c>
       <c r="J2" t="n">
-        <v>-17.12</v>
+        <v>-2.22</v>
       </c>
       <c r="K2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -536,29 +536,29 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2024-05-01 -&gt; 2026-05-23</t>
+          <t>2025-05-23 -&gt; 2026-05-23</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>43</v>
+        <v>18</v>
       </c>
       <c r="E3" t="n">
-        <v>55.8</v>
+        <v>44.4</v>
       </c>
       <c r="F3" t="n">
-        <v>3570.18</v>
+        <v>328.07</v>
       </c>
       <c r="G3" t="n">
-        <v>4070.18</v>
+        <v>828.0700000000001</v>
       </c>
       <c r="H3" t="n">
-        <v>74.59999999999999</v>
+        <v>11.8</v>
       </c>
       <c r="I3" t="n">
-        <v>2.36</v>
+        <v>2.64</v>
       </c>
       <c r="J3" t="n">
-        <v>83.03</v>
+        <v>18.23</v>
       </c>
       <c r="K3" t="b">
         <v>0</v>
@@ -575,7 +575,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -626,7 +626,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Real M15 OHLC from ejtraderLabs/historical-data (GitHub). Coverage ends 2022-03. 'Last year' = most recent real year available in-sandbox.</t>
+          <t>Real HOURLY (H1) OHLC from FeziweMelvin/XAUUSD-Gold-Price (GitHub). Coverage ends 2025-06-06 (~$3,360). No 2026 gold is reachable from the sandbox allowlist; this is the most recent real year available.</t>
         </is>
       </c>
     </row>
@@ -638,53 +638,65 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Real DAILY CLOSE only from CoinMetrics. No intraday highs/lows =&gt; SL/TP can only trigger on a daily close crossing the level. LOW fidelity; treat as illustrative.</t>
+          <t>Real DAILY CLOSE only from CoinMetrics, through 2026-05 (includes 2026). No intraday highs/lows =&gt; SL/TP can only trigger on a daily close crossing the level. LOW fidelity; treat as illustrative.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Costs modeled</t>
+          <t>Risk management</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Spread + slippage + commission are ESTIMATES of Exness-style costs, not a live feed. Real fills, slippage and swaps will differ and are usually worse.</t>
+          <t>Each trade is SIZED so the initial stop loses &lt;= risk_per_trade (5%) of equity (the 'Risk $' column). Stop moves to breakeven at +1R, then trails. Trades that cannot be sized within the 5% cap at min lot are SKIPPED.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Leverage note</t>
+          <t>Costs modeled</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1:2000 leverage does not reduce risk - it enables ruin. The requested fixed lots (0.10 XAU / 0.06 BTC) on $500 are very large relative to capital; see Max Drawdown and the 'ruined' flag.</t>
+          <t>Spread + slippage + commission are ESTIMATES of Exness-style costs, not a live feed. Real fills, slippage and swaps will differ and are usually worse.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Win rate trap</t>
+          <t>Leverage note</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A high win rate does NOT mean profitable. Read Net P/L, Profit Factor and Max Drawdown together, never win rate alone.</t>
+          <t>1:2000 leverage does not reduce risk - it enables ruin. Risk-based sizing (not fixed lots) is what keeps per-trade loss bounded; leverage just lets the margin fit.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
+          <t>Win rate trap</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A high win rate does NOT mean profitable. Read Net P/L, Profit Factor and Max Drawdown together, never win rate alone.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
           <t>Before any real money</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B11" t="inlineStr">
         <is>
           <t>Re-run on YOUR broker's data, then forward-test on a DEMO account for weeks. If demo != backtest, the cost model is wrong.</t>
         </is>
@@ -701,7 +713,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J33"/>
+  <dimension ref="A1:K145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -747,10 +759,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Risk $</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>P/L $</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Balance $</t>
         </is>
@@ -758,7 +775,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44026.5625</v>
+        <v>45492.66666666666</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -766,71 +783,77 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>1793.6</v>
+        <v>2403.82</v>
       </c>
       <c r="D2" t="n">
-        <v>1788.52</v>
+        <v>2396.35</v>
       </c>
       <c r="E2" t="n">
-        <v>1801.02</v>
+        <v>2396.12</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>44026.64583333334</v>
+        <v>45492.66666666666</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I2" t="n">
-        <v>73.40000000000001</v>
+        <v>22.43</v>
       </c>
       <c r="J2" t="n">
-        <v>573.4</v>
+        <v>-23.31</v>
+      </c>
+      <c r="K2" t="n">
+        <v>476.69</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>44026.72916666666</v>
+        <v>45492.75</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1806.1</v>
+        <v>2398.15</v>
       </c>
       <c r="D3" t="n">
-        <v>1814.42</v>
+        <v>2390.5</v>
       </c>
       <c r="E3" t="n">
-        <v>1808.54</v>
+        <v>2400.43</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>44027.27083333334</v>
+        <v>45492.79166666666</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I3" t="n">
-        <v>-25.1</v>
+        <v>22.95</v>
       </c>
       <c r="J3" t="n">
-        <v>548.3</v>
+        <v>6.63</v>
+      </c>
+      <c r="K3" t="n">
+        <v>483.31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>44027.30208333334</v>
+        <v>45495.66666666666</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -838,124 +861,133 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>1807.18</v>
+        <v>2394.32</v>
       </c>
       <c r="D4" t="n">
-        <v>1804.5</v>
+        <v>2388.78</v>
       </c>
       <c r="E4" t="n">
-        <v>1810.98</v>
+        <v>2394.27</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>44027.44791666666</v>
+        <v>45495.70833333334</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I4" t="n">
-        <v>37.27</v>
+        <v>22.15</v>
       </c>
       <c r="J4" t="n">
-        <v>585.5700000000001</v>
+        <v>-0.47</v>
+      </c>
+      <c r="K4" t="n">
+        <v>482.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>44027.46875</v>
+        <v>45495.79166666666</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>1811.91</v>
+        <v>2386.4</v>
       </c>
       <c r="D5" t="n">
-        <v>1815.29</v>
+        <v>2380.01</v>
       </c>
       <c r="E5" t="n">
-        <v>1807.06</v>
+        <v>2397.26</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>44027.55208333334</v>
+        <v>45496.20833333334</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I5" t="n">
-        <v>47.77</v>
+        <v>19.19</v>
       </c>
       <c r="J5" t="n">
-        <v>633.34</v>
+        <v>32.35</v>
+      </c>
+      <c r="K5" t="n">
+        <v>515.1900000000001</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>44027.59375</v>
+        <v>45496.5</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>1804.18</v>
+        <v>2403.68</v>
       </c>
       <c r="D6" t="n">
-        <v>1799.88</v>
+        <v>2408.88</v>
       </c>
       <c r="E6" t="n">
-        <v>1810.42</v>
+        <v>2409.1</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>44027.71875</v>
+        <v>45496.58333333334</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I6" t="n">
-        <v>61.66</v>
+        <v>20.77</v>
       </c>
       <c r="J6" t="n">
-        <v>695</v>
+        <v>-21.95</v>
+      </c>
+      <c r="K6" t="n">
+        <v>493.24</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>44028.22916666666</v>
+        <v>45497.25</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>1809.33</v>
+        <v>2413.83</v>
       </c>
       <c r="D7" t="n">
-        <v>1806.92</v>
+        <v>2418.67</v>
       </c>
       <c r="E7" t="n">
-        <v>1806.7</v>
+        <v>2418.89</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>44028.38541666666</v>
+        <v>45497.375</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -963,35 +995,38 @@
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.1</v>
+        <v>0.05</v>
       </c>
       <c r="I7" t="n">
-        <v>-27.06</v>
+        <v>24.22</v>
       </c>
       <c r="J7" t="n">
-        <v>667.9400000000001</v>
+        <v>-25.7</v>
+      </c>
+      <c r="K7" t="n">
+        <v>467.54</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>44028.40625</v>
+        <v>45497.66666666666</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>1806.36</v>
+        <v>2421.12</v>
       </c>
       <c r="D8" t="n">
-        <v>1804.01</v>
+        <v>2426.16</v>
       </c>
       <c r="E8" t="n">
-        <v>1803.78</v>
+        <v>2426.38</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>44028.53125</v>
+        <v>45497.66666666666</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -999,54 +1034,60 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I8" t="n">
-        <v>-26.51</v>
+        <v>20.14</v>
       </c>
       <c r="J8" t="n">
-        <v>641.4299999999999</v>
+        <v>-21.32</v>
+      </c>
+      <c r="K8" t="n">
+        <v>446.22</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>44028.8125</v>
+        <v>45497.75</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>1803.64</v>
+        <v>2430.02</v>
       </c>
       <c r="D9" t="n">
-        <v>1799.13</v>
+        <v>2436.64</v>
       </c>
       <c r="E9" t="n">
-        <v>1798.91</v>
+        <v>2403.8</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>44028.83333333334</v>
+        <v>45497.91666666666</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I9" t="n">
-        <v>-47.99</v>
+        <v>19.84</v>
       </c>
       <c r="J9" t="n">
-        <v>593.4400000000001</v>
+        <v>78.45999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>524.6799999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>44028.85416666666</v>
+        <v>45498.04166666666</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
@@ -1054,16 +1095,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>1800.44</v>
+        <v>2397.28</v>
       </c>
       <c r="D10" t="n">
-        <v>1795.55</v>
+        <v>2389.89</v>
       </c>
       <c r="E10" t="n">
-        <v>1795.32</v>
+        <v>2389.66</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>44028.94791666666</v>
+        <v>45498.16666666666</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -1071,90 +1112,99 @@
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I10" t="n">
-        <v>-51.91</v>
+        <v>22.17</v>
       </c>
       <c r="J10" t="n">
-        <v>541.53</v>
+        <v>-23.05</v>
+      </c>
+      <c r="K10" t="n">
+        <v>501.63</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>44029.42708333334</v>
+        <v>45498.25</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1800.22</v>
+        <v>2372.74</v>
       </c>
       <c r="D11" t="n">
-        <v>1801.94</v>
+        <v>2363.49</v>
       </c>
       <c r="E11" t="n">
-        <v>1802.17</v>
+        <v>2372.92</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>44029.46875</v>
+        <v>45498.58333333334</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I11" t="n">
-        <v>-20.12</v>
+        <v>18.51</v>
       </c>
       <c r="J11" t="n">
-        <v>521.41</v>
+        <v>0.21</v>
+      </c>
+      <c r="K11" t="n">
+        <v>501.84</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>44029.48958333334</v>
+        <v>45498.875</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>1801.5</v>
+        <v>2356.26</v>
       </c>
       <c r="D12" t="n">
-        <v>1803.84</v>
+        <v>2346.7</v>
       </c>
       <c r="E12" t="n">
-        <v>1804.06</v>
+        <v>2369.39</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>44029.54166666666</v>
+        <v>45499.33333333334</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>-26.29</v>
+        <v>19.13</v>
       </c>
       <c r="J12" t="n">
-        <v>495.11</v>
+        <v>26.11</v>
+      </c>
+      <c r="K12" t="n">
+        <v>527.95</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>44029.5625</v>
+        <v>45499.70833333334</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -1162,16 +1212,16 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>1803.92</v>
+        <v>2380.84</v>
       </c>
       <c r="D13" t="n">
-        <v>1806.49</v>
+        <v>2387.51</v>
       </c>
       <c r="E13" t="n">
-        <v>1806.72</v>
+        <v>2387.74</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>44029.61458333334</v>
+        <v>45499.70833333334</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -1179,18 +1229,21 @@
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I13" t="n">
-        <v>-28.71</v>
+        <v>20.04</v>
       </c>
       <c r="J13" t="n">
-        <v>466.41</v>
+        <v>-20.92</v>
+      </c>
+      <c r="K13" t="n">
+        <v>507.03</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>44029.64583333334</v>
+        <v>45499.79166666666</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -1198,16 +1251,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>1807.1</v>
+        <v>2384.86</v>
       </c>
       <c r="D14" t="n">
-        <v>1809.35</v>
+        <v>2391.28</v>
       </c>
       <c r="E14" t="n">
-        <v>1809.57</v>
+        <v>2391.51</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>44029.67708333334</v>
+        <v>45502.04166666666</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1215,71 +1268,77 @@
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I14" t="n">
-        <v>-25.46</v>
+        <v>19.28</v>
       </c>
       <c r="J14" t="n">
-        <v>440.94</v>
+        <v>-20.17</v>
+      </c>
+      <c r="K14" t="n">
+        <v>486.86</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>44032.17708333334</v>
+        <v>45502.125</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>1806.4</v>
+        <v>2396.74</v>
       </c>
       <c r="D15" t="n">
-        <v>1803.74</v>
+        <v>2403.24</v>
       </c>
       <c r="E15" t="n">
-        <v>1810.16</v>
+        <v>2395.31</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>44032.39583333334</v>
+        <v>45502.25</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I15" t="n">
-        <v>36.91</v>
+        <v>19.48</v>
       </c>
       <c r="J15" t="n">
-        <v>477.85</v>
+        <v>4.09</v>
+      </c>
+      <c r="K15" t="n">
+        <v>490.95</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>44032.5</v>
+        <v>45502.75</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>1811.71</v>
+        <v>2381.36</v>
       </c>
       <c r="D16" t="n">
-        <v>1814.93</v>
+        <v>2375.09</v>
       </c>
       <c r="E16" t="n">
-        <v>1815.15</v>
+        <v>2374.86</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>44032.61458333334</v>
+        <v>45502.75</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1287,54 +1346,60 @@
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I16" t="n">
-        <v>-35.16</v>
+        <v>18.8</v>
       </c>
       <c r="J16" t="n">
-        <v>442.69</v>
+        <v>-19.69</v>
+      </c>
+      <c r="K16" t="n">
+        <v>471.27</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>44032.63541666666</v>
+        <v>45502.83333333334</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>1813.78</v>
+        <v>2378.32</v>
       </c>
       <c r="D17" t="n">
-        <v>1816.63</v>
+        <v>2372.04</v>
       </c>
       <c r="E17" t="n">
-        <v>1816.86</v>
+        <v>2378.83</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>44032.64583333334</v>
+        <v>45503.16666666666</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I17" t="n">
-        <v>-31.44</v>
+        <v>18.85</v>
       </c>
       <c r="J17" t="n">
-        <v>411.25</v>
+        <v>1.31</v>
+      </c>
+      <c r="K17" t="n">
+        <v>472.57</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>44032.67708333334</v>
+        <v>45503.58333333334</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
@@ -1342,35 +1407,38 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1815.44</v>
+        <v>2391.3</v>
       </c>
       <c r="D18" t="n">
-        <v>1818.94</v>
+        <v>2394.92</v>
       </c>
       <c r="E18" t="n">
-        <v>1819.16</v>
+        <v>2389.52</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>44032.72916666666</v>
+        <v>45503.66666666666</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="I18" t="n">
-        <v>-37.96</v>
+        <v>21.78</v>
       </c>
       <c r="J18" t="n">
-        <v>373.29</v>
+        <v>10.2</v>
+      </c>
+      <c r="K18" t="n">
+        <v>482.78</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>44033.28125</v>
+        <v>45503.83333333334</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -1378,16 +1446,16 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>1819.56</v>
+        <v>2399.54</v>
       </c>
       <c r="D19" t="n">
-        <v>1822</v>
+        <v>2405.21</v>
       </c>
       <c r="E19" t="n">
-        <v>1822.23</v>
+        <v>2405.44</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>44033.40625</v>
+        <v>45503.83333333334</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1395,18 +1463,21 @@
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.1</v>
+        <v>0.04</v>
       </c>
       <c r="I19" t="n">
-        <v>-27.31</v>
+        <v>22.68</v>
       </c>
       <c r="J19" t="n">
-        <v>345.98</v>
+        <v>-23.86</v>
+      </c>
+      <c r="K19" t="n">
+        <v>458.92</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="n">
-        <v>44033.42708333334</v>
+        <v>45503.91666666666</v>
       </c>
       <c r="B20" t="inlineStr">
         <is>
@@ -1414,16 +1485,16 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>1823.06</v>
+        <v>2404.56</v>
       </c>
       <c r="D20" t="n">
-        <v>1826.52</v>
+        <v>2410.78</v>
       </c>
       <c r="E20" t="n">
-        <v>1826.75</v>
+        <v>2411</v>
       </c>
       <c r="F20" s="1" t="n">
-        <v>44033.57291666666</v>
+        <v>45503.95833333334</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1431,18 +1502,21 @@
         </is>
       </c>
       <c r="H20" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I20" t="n">
-        <v>-37.64</v>
+        <v>18.63</v>
       </c>
       <c r="J20" t="n">
-        <v>308.34</v>
+        <v>-19.52</v>
+      </c>
+      <c r="K20" t="n">
+        <v>439.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="n">
-        <v>44033.59375</v>
+        <v>45504.08333333334</v>
       </c>
       <c r="B21" t="inlineStr">
         <is>
@@ -1450,16 +1524,16 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>1826.9</v>
+        <v>2408.87</v>
       </c>
       <c r="D21" t="n">
-        <v>1829.95</v>
+        <v>2415.3</v>
       </c>
       <c r="E21" t="n">
-        <v>1830.18</v>
+        <v>2415.52</v>
       </c>
       <c r="F21" s="1" t="n">
-        <v>44033.625</v>
+        <v>45504.25</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1467,18 +1541,21 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I21" t="n">
-        <v>-33.54</v>
+        <v>19.3</v>
       </c>
       <c r="J21" t="n">
-        <v>274.81</v>
+        <v>-20.19</v>
+      </c>
+      <c r="K21" t="n">
+        <v>419.21</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="n">
-        <v>44033.64583333334</v>
+        <v>45504.33333333334</v>
       </c>
       <c r="B22" t="inlineStr">
         <is>
@@ -1486,16 +1563,16 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>1838.8</v>
+        <v>2420.87</v>
       </c>
       <c r="D22" t="n">
-        <v>1843.61</v>
+        <v>2427.78</v>
       </c>
       <c r="E22" t="n">
-        <v>1843.83</v>
+        <v>2428.01</v>
       </c>
       <c r="F22" s="1" t="n">
-        <v>44034.08333333334</v>
+        <v>45504.70833333334</v>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1503,18 +1580,21 @@
         </is>
       </c>
       <c r="H22" t="n">
-        <v>0.1</v>
+        <v>0.03</v>
       </c>
       <c r="I22" t="n">
-        <v>-51.08</v>
+        <v>20.76</v>
       </c>
       <c r="J22" t="n">
-        <v>223.73</v>
+        <v>-21.64</v>
+      </c>
+      <c r="K22" t="n">
+        <v>397.57</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="n">
-        <v>44034.17708333334</v>
+        <v>45504.83333333334</v>
       </c>
       <c r="B23" t="inlineStr">
         <is>
@@ -1522,35 +1602,38 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>1865.17</v>
+        <v>2426.68</v>
       </c>
       <c r="D23" t="n">
-        <v>1872.51</v>
+        <v>2433.39</v>
       </c>
       <c r="E23" t="n">
-        <v>1854.38</v>
+        <v>2433.61</v>
       </c>
       <c r="F23" s="1" t="n">
-        <v>44034.3125</v>
+        <v>45504.875</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I23" t="n">
-        <v>107.17</v>
+        <v>13.41</v>
       </c>
       <c r="J23" t="n">
-        <v>330.9</v>
+        <v>-14</v>
+      </c>
+      <c r="K23" t="n">
+        <v>383.57</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="n">
-        <v>44034.79166666666</v>
+        <v>45504.95833333334</v>
       </c>
       <c r="B24" t="inlineStr">
         <is>
@@ -1558,16 +1641,16 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>1863.93</v>
+        <v>2449.54</v>
       </c>
       <c r="D24" t="n">
-        <v>1872.78</v>
+        <v>2457.24</v>
       </c>
       <c r="E24" t="n">
-        <v>1873</v>
+        <v>2457.46</v>
       </c>
       <c r="F24" s="1" t="n">
-        <v>44035.04166666666</v>
+        <v>45505.16666666666</v>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1575,18 +1658,21 @@
         </is>
       </c>
       <c r="H24" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I24" t="n">
-        <v>-91.48</v>
+        <v>15.38</v>
       </c>
       <c r="J24" t="n">
-        <v>239.42</v>
+        <v>-15.97</v>
+      </c>
+      <c r="K24" t="n">
+        <v>367.6</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="n">
-        <v>44035.41666666666</v>
+        <v>45506.25</v>
       </c>
       <c r="B25" t="inlineStr">
         <is>
@@ -1594,16 +1680,16 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>1875.41</v>
+        <v>2455.24</v>
       </c>
       <c r="D25" t="n">
-        <v>1879.74</v>
+        <v>2464.05</v>
       </c>
       <c r="E25" t="n">
-        <v>1879.96</v>
+        <v>2464.27</v>
       </c>
       <c r="F25" s="1" t="n">
-        <v>44035.45833333334</v>
+        <v>45506.33333333334</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1611,18 +1697,21 @@
         </is>
       </c>
       <c r="H25" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I25" t="n">
-        <v>-46.26</v>
+        <v>17.6</v>
       </c>
       <c r="J25" t="n">
-        <v>193.16</v>
+        <v>-18.19</v>
+      </c>
+      <c r="K25" t="n">
+        <v>349.41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="n">
-        <v>44035.47916666666</v>
+        <v>45506.41666666666</v>
       </c>
       <c r="B26" t="inlineStr">
         <is>
@@ -1630,124 +1719,133 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1880.8</v>
+        <v>2465.22</v>
       </c>
       <c r="D26" t="n">
-        <v>1886.35</v>
+        <v>2472.37</v>
       </c>
       <c r="E26" t="n">
-        <v>1886.57</v>
+        <v>2464.89</v>
       </c>
       <c r="F26" s="1" t="n">
-        <v>44035.47916666666</v>
+        <v>45506.625</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I26" t="n">
-        <v>-58.49</v>
+        <v>14.29</v>
       </c>
       <c r="J26" t="n">
-        <v>134.66</v>
+        <v>0.53</v>
+      </c>
+      <c r="K26" t="n">
+        <v>349.94</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
-        <v>44035.5</v>
+        <v>45506.75</v>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>1882.1</v>
+        <v>2431.68</v>
       </c>
       <c r="D27" t="n">
-        <v>1889.25</v>
+        <v>2419.82</v>
       </c>
       <c r="E27" t="n">
-        <v>1871.59</v>
+        <v>2419.6</v>
       </c>
       <c r="F27" s="1" t="n">
-        <v>44035.66666666666</v>
+        <v>45506.75</v>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I27" t="n">
-        <v>104.39</v>
+        <v>11.86</v>
       </c>
       <c r="J27" t="n">
-        <v>239.05</v>
+        <v>-12.16</v>
+      </c>
+      <c r="K27" t="n">
+        <v>337.78</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
-        <v>44035.77083333334</v>
+        <v>45506.83333333334</v>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>1893.48</v>
+        <v>2430.57</v>
       </c>
       <c r="D28" t="n">
-        <v>1903.9</v>
+        <v>2417.79</v>
       </c>
       <c r="E28" t="n">
-        <v>1888.33</v>
+        <v>2434.34</v>
       </c>
       <c r="F28" s="1" t="n">
-        <v>44036.3125</v>
+        <v>45509.125</v>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>TIME</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I28" t="n">
-        <v>50.8</v>
+        <v>12.78</v>
       </c>
       <c r="J28" t="n">
-        <v>289.85</v>
+        <v>3.7</v>
+      </c>
+      <c r="K28" t="n">
+        <v>341.48</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
-        <v>44036.38541666666</v>
+        <v>45509.58333333334</v>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>1888.96</v>
+        <v>2408.66</v>
       </c>
       <c r="D29" t="n">
-        <v>1894.4</v>
+        <v>2394.5</v>
       </c>
       <c r="E29" t="n">
-        <v>1894.62</v>
+        <v>2394.28</v>
       </c>
       <c r="F29" s="1" t="n">
-        <v>44036.42708333334</v>
+        <v>45509.58333333334</v>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1755,71 +1853,77 @@
         </is>
       </c>
       <c r="H29" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I29" t="n">
-        <v>-57.36</v>
+        <v>14.16</v>
       </c>
       <c r="J29" t="n">
-        <v>232.49</v>
+        <v>-14.46</v>
+      </c>
+      <c r="K29" t="n">
+        <v>327.02</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
-        <v>44036.44791666666</v>
+        <v>45510.66666666666</v>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>1894.8</v>
+        <v>2393.13</v>
       </c>
       <c r="D30" t="n">
-        <v>1901.07</v>
+        <v>2384.32</v>
       </c>
       <c r="E30" t="n">
-        <v>1901.3</v>
+        <v>2393.99</v>
       </c>
       <c r="F30" s="1" t="n">
-        <v>44036.66666666666</v>
+        <v>45510.75</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I30" t="n">
-        <v>-65.61</v>
+        <v>8.81</v>
       </c>
       <c r="J30" t="n">
-        <v>166.88</v>
+        <v>0.79</v>
+      </c>
+      <c r="K30" t="n">
+        <v>327.81</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
-        <v>44036.6875</v>
+        <v>45510.83333333334</v>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>1905.45</v>
+        <v>2390.12</v>
       </c>
       <c r="D31" t="n">
-        <v>1913.31</v>
+        <v>2380.67</v>
       </c>
       <c r="E31" t="n">
-        <v>1913.54</v>
+        <v>2380.45</v>
       </c>
       <c r="F31" s="1" t="n">
-        <v>44039.09375</v>
+        <v>45511.16666666666</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1827,18 +1931,21 @@
         </is>
       </c>
       <c r="H31" t="n">
-        <v>0.1</v>
+        <v>0.01</v>
       </c>
       <c r="I31" t="n">
-        <v>-81.62</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="J31" t="n">
-        <v>85.26000000000001</v>
+        <v>-9.75</v>
+      </c>
+      <c r="K31" t="n">
+        <v>318.06</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
-        <v>44039.11458333334</v>
+        <v>45511.58333333334</v>
       </c>
       <c r="B32" t="inlineStr">
         <is>
@@ -1846,16 +1953,16 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>1914.22</v>
+        <v>2397.12</v>
       </c>
       <c r="D32" t="n">
-        <v>1919.49</v>
+        <v>2403.31</v>
       </c>
       <c r="E32" t="n">
-        <v>1919.71</v>
+        <v>2403.53</v>
       </c>
       <c r="F32" s="1" t="n">
-        <v>44039.19791666666</v>
+        <v>45511.625</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1863,18 +1970,21 @@
         </is>
       </c>
       <c r="H32" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I32" t="n">
-        <v>-55.68</v>
+        <v>12.38</v>
       </c>
       <c r="J32" t="n">
-        <v>29.58</v>
+        <v>-12.97</v>
+      </c>
+      <c r="K32" t="n">
+        <v>305.08</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="n">
-        <v>44039.23958333334</v>
+        <v>45512.58333333334</v>
       </c>
       <c r="B33" t="inlineStr">
         <is>
@@ -1882,16 +1992,16 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>1926.06</v>
+        <v>2405</v>
       </c>
       <c r="D33" t="n">
-        <v>1933.51</v>
+        <v>2410.38</v>
       </c>
       <c r="E33" t="n">
-        <v>1933.73</v>
+        <v>2410.6</v>
       </c>
       <c r="F33" s="1" t="n">
-        <v>44039.25</v>
+        <v>45512.58333333334</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1899,13 +2009,4384 @@
         </is>
       </c>
       <c r="H33" t="n">
-        <v>0.1</v>
+        <v>0.02</v>
       </c>
       <c r="I33" t="n">
-        <v>-77.48999999999999</v>
+        <v>10.76</v>
       </c>
       <c r="J33" t="n">
-        <v>-47.91</v>
+        <v>-11.35</v>
+      </c>
+      <c r="K33" t="n">
+        <v>293.73</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="n">
+        <v>45512.66666666666</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>2407.76</v>
+      </c>
+      <c r="D34" t="n">
+        <v>2413.72</v>
+      </c>
+      <c r="E34" t="n">
+        <v>2413.95</v>
+      </c>
+      <c r="F34" s="1" t="n">
+        <v>45512.66666666666</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H34" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I34" t="n">
+        <v>11.93</v>
+      </c>
+      <c r="J34" t="n">
+        <v>-12.52</v>
+      </c>
+      <c r="K34" t="n">
+        <v>281.21</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="n">
+        <v>45512.75</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>2413.42</v>
+      </c>
+      <c r="D35" t="n">
+        <v>2420.78</v>
+      </c>
+      <c r="E35" t="n">
+        <v>2421</v>
+      </c>
+      <c r="F35" s="1" t="n">
+        <v>45512.79166666666</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H35" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I35" t="n">
+        <v>7.36</v>
+      </c>
+      <c r="J35" t="n">
+        <v>-7.66</v>
+      </c>
+      <c r="K35" t="n">
+        <v>273.55</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="n">
+        <v>45512.875</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>2423.2</v>
+      </c>
+      <c r="D36" t="n">
+        <v>2431.1</v>
+      </c>
+      <c r="E36" t="n">
+        <v>2431.33</v>
+      </c>
+      <c r="F36" s="1" t="n">
+        <v>45513.54166666666</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H36" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I36" t="n">
+        <v>7.91</v>
+      </c>
+      <c r="J36" t="n">
+        <v>-8.199999999999999</v>
+      </c>
+      <c r="K36" t="n">
+        <v>265.35</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="n">
+        <v>45513.66666666666</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>2429.34</v>
+      </c>
+      <c r="D37" t="n">
+        <v>2434.78</v>
+      </c>
+      <c r="E37" t="n">
+        <v>2426.63</v>
+      </c>
+      <c r="F37" s="1" t="n">
+        <v>45513.70833333334</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H37" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I37" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="J37" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="K37" t="n">
+        <v>270.61</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="n">
+        <v>45513.79166666666</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>2431.12</v>
+      </c>
+      <c r="D38" t="n">
+        <v>2437.63</v>
+      </c>
+      <c r="E38" t="n">
+        <v>2430.48</v>
+      </c>
+      <c r="F38" s="1" t="n">
+        <v>45516.29166666666</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H38" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I38" t="n">
+        <v>13.01</v>
+      </c>
+      <c r="J38" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="K38" t="n">
+        <v>271.77</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="n">
+        <v>45516.375</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>2434.34</v>
+      </c>
+      <c r="D39" t="n">
+        <v>2438.93</v>
+      </c>
+      <c r="E39" t="n">
+        <v>2439.16</v>
+      </c>
+      <c r="F39" s="1" t="n">
+        <v>45516.41666666666</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H39" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I39" t="n">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="J39" t="n">
+        <v>-9.789999999999999</v>
+      </c>
+      <c r="K39" t="n">
+        <v>261.98</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="n">
+        <v>45516.5</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>2441.64</v>
+      </c>
+      <c r="D40" t="n">
+        <v>2445.9</v>
+      </c>
+      <c r="E40" t="n">
+        <v>2446.12</v>
+      </c>
+      <c r="F40" s="1" t="n">
+        <v>45516.66666666666</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H40" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="I40" t="n">
+        <v>12.76</v>
+      </c>
+      <c r="J40" t="n">
+        <v>-13.65</v>
+      </c>
+      <c r="K40" t="n">
+        <v>248.33</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="n">
+        <v>45516.75</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>2453.06</v>
+      </c>
+      <c r="D41" t="n">
+        <v>2458.89</v>
+      </c>
+      <c r="E41" t="n">
+        <v>2459.11</v>
+      </c>
+      <c r="F41" s="1" t="n">
+        <v>45516.75</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H41" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I41" t="n">
+        <v>11.67</v>
+      </c>
+      <c r="J41" t="n">
+        <v>-12.26</v>
+      </c>
+      <c r="K41" t="n">
+        <v>236.07</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="n">
+        <v>45516.83333333334</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>2462.81</v>
+      </c>
+      <c r="D42" t="n">
+        <v>2469.03</v>
+      </c>
+      <c r="E42" t="n">
+        <v>2469.26</v>
+      </c>
+      <c r="F42" s="1" t="n">
+        <v>45516.875</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H42" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I42" t="n">
+        <v>6.23</v>
+      </c>
+      <c r="J42" t="n">
+        <v>-6.52</v>
+      </c>
+      <c r="K42" t="n">
+        <v>229.55</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="1" t="n">
+        <v>45516.95833333334</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>2470.14</v>
+      </c>
+      <c r="D43" t="n">
+        <v>2476.29</v>
+      </c>
+      <c r="E43" t="n">
+        <v>2476.51</v>
+      </c>
+      <c r="F43" s="1" t="n">
+        <v>45517.125</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H43" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I43" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="J43" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="K43" t="n">
+        <v>223.11</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="1" t="n">
+        <v>45518.25</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>2460.05</v>
+      </c>
+      <c r="D44" t="n">
+        <v>2453.62</v>
+      </c>
+      <c r="E44" t="n">
+        <v>2471.92</v>
+      </c>
+      <c r="F44" s="1" t="n">
+        <v>45518.5</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H44" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I44" t="n">
+        <v>6.43</v>
+      </c>
+      <c r="J44" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K44" t="n">
+        <v>234.91</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="1" t="n">
+        <v>45518.58333333334</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>2474.66</v>
+      </c>
+      <c r="D45" t="n">
+        <v>2479.83</v>
+      </c>
+      <c r="E45" t="n">
+        <v>2467.77</v>
+      </c>
+      <c r="F45" s="1" t="n">
+        <v>45518.66666666666</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H45" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I45" t="n">
+        <v>10.33</v>
+      </c>
+      <c r="J45" t="n">
+        <v>13.65</v>
+      </c>
+      <c r="K45" t="n">
+        <v>248.56</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="1" t="n">
+        <v>45518.75</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>2450.36</v>
+      </c>
+      <c r="D46" t="n">
+        <v>2442.33</v>
+      </c>
+      <c r="E46" t="n">
+        <v>2442.11</v>
+      </c>
+      <c r="F46" s="1" t="n">
+        <v>45518.75</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H46" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I46" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="J46" t="n">
+        <v>-8.32</v>
+      </c>
+      <c r="K46" t="n">
+        <v>240.24</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="1" t="n">
+        <v>45518.83333333334</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>2444.32</v>
+      </c>
+      <c r="D47" t="n">
+        <v>2436.36</v>
+      </c>
+      <c r="E47" t="n">
+        <v>2455.87</v>
+      </c>
+      <c r="F47" s="1" t="n">
+        <v>45519.625</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H47" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I47" t="n">
+        <v>7.97</v>
+      </c>
+      <c r="J47" t="n">
+        <v>11.47</v>
+      </c>
+      <c r="K47" t="n">
+        <v>251.72</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="1" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>2463.04</v>
+      </c>
+      <c r="D48" t="n">
+        <v>2467.45</v>
+      </c>
+      <c r="E48" t="n">
+        <v>2467.68</v>
+      </c>
+      <c r="F48" s="1" t="n">
+        <v>45520.54166666666</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H48" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I48" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="J48" t="n">
+        <v>-9.43</v>
+      </c>
+      <c r="K48" t="n">
+        <v>242.29</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="1" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>2471.83</v>
+      </c>
+      <c r="D49" t="n">
+        <v>2476.45</v>
+      </c>
+      <c r="E49" t="n">
+        <v>2476.68</v>
+      </c>
+      <c r="F49" s="1" t="n">
+        <v>45520.625</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H49" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I49" t="n">
+        <v>9.25</v>
+      </c>
+      <c r="J49" t="n">
+        <v>-9.84</v>
+      </c>
+      <c r="K49" t="n">
+        <v>232.45</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="1" t="n">
+        <v>45520.70833333334</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>2493.95</v>
+      </c>
+      <c r="D50" t="n">
+        <v>2500.85</v>
+      </c>
+      <c r="E50" t="n">
+        <v>2484.56</v>
+      </c>
+      <c r="F50" s="1" t="n">
+        <v>45520.75</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H50" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I50" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="J50" t="n">
+        <v>9.32</v>
+      </c>
+      <c r="K50" t="n">
+        <v>241.76</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="1" t="n">
+        <v>45520.83333333334</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>2495.58</v>
+      </c>
+      <c r="D51" t="n">
+        <v>2503.83</v>
+      </c>
+      <c r="E51" t="n">
+        <v>2504.06</v>
+      </c>
+      <c r="F51" s="1" t="n">
+        <v>45520.875</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H51" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I51" t="n">
+        <v>8.26</v>
+      </c>
+      <c r="J51" t="n">
+        <v>-8.550000000000001</v>
+      </c>
+      <c r="K51" t="n">
+        <v>233.21</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="n">
+        <v>45520.95833333334</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>2507.68</v>
+      </c>
+      <c r="D52" t="n">
+        <v>2516.72</v>
+      </c>
+      <c r="E52" t="n">
+        <v>2504.16</v>
+      </c>
+      <c r="F52" s="1" t="n">
+        <v>45523.25</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H52" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I52" t="n">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="J52" t="n">
+        <v>3.44</v>
+      </c>
+      <c r="K52" t="n">
+        <v>236.65</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="n">
+        <v>45524.45833333334</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>2514.64</v>
+      </c>
+      <c r="D53" t="n">
+        <v>2521.5</v>
+      </c>
+      <c r="E53" t="n">
+        <v>2521.72</v>
+      </c>
+      <c r="F53" s="1" t="n">
+        <v>45524.45833333334</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H53" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I53" t="n">
+        <v>6.86</v>
+      </c>
+      <c r="J53" t="n">
+        <v>-7.16</v>
+      </c>
+      <c r="K53" t="n">
+        <v>229.5</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="n">
+        <v>45524.54166666666</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>2521.46</v>
+      </c>
+      <c r="D54" t="n">
+        <v>2529.04</v>
+      </c>
+      <c r="E54" t="n">
+        <v>2529.26</v>
+      </c>
+      <c r="F54" s="1" t="n">
+        <v>45524.625</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H54" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I54" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="J54" t="n">
+        <v>-7.87</v>
+      </c>
+      <c r="K54" t="n">
+        <v>221.63</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="n">
+        <v>45526.70833333334</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>2488.11</v>
+      </c>
+      <c r="D55" t="n">
+        <v>2477.94</v>
+      </c>
+      <c r="E55" t="n">
+        <v>2477.72</v>
+      </c>
+      <c r="F55" s="1" t="n">
+        <v>45526.70833333334</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H55" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I55" t="n">
+        <v>10.17</v>
+      </c>
+      <c r="J55" t="n">
+        <v>-10.47</v>
+      </c>
+      <c r="K55" t="n">
+        <v>211.16</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="n">
+        <v>45534.79166666666</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>2502.58</v>
+      </c>
+      <c r="D56" t="n">
+        <v>2492.5</v>
+      </c>
+      <c r="E56" t="n">
+        <v>2492.27</v>
+      </c>
+      <c r="F56" s="1" t="n">
+        <v>45537.20833333334</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H56" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I56" t="n">
+        <v>10.09</v>
+      </c>
+      <c r="J56" t="n">
+        <v>-10.38</v>
+      </c>
+      <c r="K56" t="n">
+        <v>200.78</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="1" t="n">
+        <v>45540.5</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>2514.38</v>
+      </c>
+      <c r="D57" t="n">
+        <v>2520.59</v>
+      </c>
+      <c r="E57" t="n">
+        <v>2520.82</v>
+      </c>
+      <c r="F57" s="1" t="n">
+        <v>45540.625</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H57" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I57" t="n">
+        <v>6.22</v>
+      </c>
+      <c r="J57" t="n">
+        <v>-6.51</v>
+      </c>
+      <c r="K57" t="n">
+        <v>194.26</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="n">
+        <v>45541.70833333334</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>2509.52</v>
+      </c>
+      <c r="D58" t="n">
+        <v>2500.77</v>
+      </c>
+      <c r="E58" t="n">
+        <v>2500.55</v>
+      </c>
+      <c r="F58" s="1" t="n">
+        <v>45541.70833333334</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H58" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I58" t="n">
+        <v>8.75</v>
+      </c>
+      <c r="J58" t="n">
+        <v>-9.050000000000001</v>
+      </c>
+      <c r="K58" t="n">
+        <v>185.22</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="1" t="n">
+        <v>45545.66666666666</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>2513.48</v>
+      </c>
+      <c r="D59" t="n">
+        <v>2519.3</v>
+      </c>
+      <c r="E59" t="n">
+        <v>2502.04</v>
+      </c>
+      <c r="F59" s="1" t="n">
+        <v>45545.70833333334</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="H59" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I59" t="n">
+        <v>5.83</v>
+      </c>
+      <c r="J59" t="n">
+        <v>11.36</v>
+      </c>
+      <c r="K59" t="n">
+        <v>196.58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="n">
+        <v>45546.66666666666</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>2508.3</v>
+      </c>
+      <c r="D60" t="n">
+        <v>2500.14</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2511.55</v>
+      </c>
+      <c r="F60" s="1" t="n">
+        <v>45546.875</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H60" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I60" t="n">
+        <v>8.16</v>
+      </c>
+      <c r="J60" t="n">
+        <v>3.18</v>
+      </c>
+      <c r="K60" t="n">
+        <v>199.76</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="n">
+        <v>45547.66666666666</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>2528.2</v>
+      </c>
+      <c r="D61" t="n">
+        <v>2535.19</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2535.42</v>
+      </c>
+      <c r="F61" s="1" t="n">
+        <v>45547.66666666666</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H61" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I61" t="n">
+        <v>6.99</v>
+      </c>
+      <c r="J61" t="n">
+        <v>-7.28</v>
+      </c>
+      <c r="K61" t="n">
+        <v>192.48</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="n">
+        <v>45552.54166666666</v>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>2573.74</v>
+      </c>
+      <c r="D62" t="n">
+        <v>2569.33</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2576.95</v>
+      </c>
+      <c r="F62" s="1" t="n">
+        <v>45552.625</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H62" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I62" t="n">
+        <v>8.81</v>
+      </c>
+      <c r="J62" t="n">
+        <v>6.29</v>
+      </c>
+      <c r="K62" t="n">
+        <v>198.77</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="1" t="n">
+        <v>45552.79166666666</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>2565.76</v>
+      </c>
+      <c r="D63" t="n">
+        <v>2558.18</v>
+      </c>
+      <c r="E63" t="n">
+        <v>2568.54</v>
+      </c>
+      <c r="F63" s="1" t="n">
+        <v>45553.29166666666</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H63" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I63" t="n">
+        <v>7.57</v>
+      </c>
+      <c r="J63" t="n">
+        <v>2.72</v>
+      </c>
+      <c r="K63" t="n">
+        <v>201.48</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="1" t="n">
+        <v>45553.95833333334</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>2549.16</v>
+      </c>
+      <c r="D64" t="n">
+        <v>2539.63</v>
+      </c>
+      <c r="E64" t="n">
+        <v>2551.76</v>
+      </c>
+      <c r="F64" s="1" t="n">
+        <v>45554.16666666666</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H64" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I64" t="n">
+        <v>9.529999999999999</v>
+      </c>
+      <c r="J64" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="K64" t="n">
+        <v>204.01</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="1" t="n">
+        <v>45554.54166666666</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>2591.5</v>
+      </c>
+      <c r="D65" t="n">
+        <v>2600.26</v>
+      </c>
+      <c r="E65" t="n">
+        <v>2582.07</v>
+      </c>
+      <c r="F65" s="1" t="n">
+        <v>45554.66666666666</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H65" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I65" t="n">
+        <v>8.76</v>
+      </c>
+      <c r="J65" t="n">
+        <v>9.359999999999999</v>
+      </c>
+      <c r="K65" t="n">
+        <v>213.37</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="n">
+        <v>45559.75</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>2643.2</v>
+      </c>
+      <c r="D66" t="n">
+        <v>2650.41</v>
+      </c>
+      <c r="E66" t="n">
+        <v>2650.64</v>
+      </c>
+      <c r="F66" s="1" t="n">
+        <v>45559.79166666666</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H66" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I66" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="J66" t="n">
+        <v>-7.5</v>
+      </c>
+      <c r="K66" t="n">
+        <v>205.86</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="1" t="n">
+        <v>45559.875</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>2653.76</v>
+      </c>
+      <c r="D67" t="n">
+        <v>2661.75</v>
+      </c>
+      <c r="E67" t="n">
+        <v>2661.97</v>
+      </c>
+      <c r="F67" s="1" t="n">
+        <v>45559.91666666666</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H67" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I67" t="n">
+        <v>7.99</v>
+      </c>
+      <c r="J67" t="n">
+        <v>-8.289999999999999</v>
+      </c>
+      <c r="K67" t="n">
+        <v>197.58</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>2672.36</v>
+      </c>
+      <c r="D68" t="n">
+        <v>2676.9</v>
+      </c>
+      <c r="E68" t="n">
+        <v>2677.13</v>
+      </c>
+      <c r="F68" s="1" t="n">
+        <v>45561.58333333334</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H68" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I68" t="n">
+        <v>9.1</v>
+      </c>
+      <c r="J68" t="n">
+        <v>-9.69</v>
+      </c>
+      <c r="K68" t="n">
+        <v>187.89</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="n">
+        <v>45561.66666666666</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>2676.9</v>
+      </c>
+      <c r="D69" t="n">
+        <v>2683.01</v>
+      </c>
+      <c r="E69" t="n">
+        <v>2661.03</v>
+      </c>
+      <c r="F69" s="1" t="n">
+        <v>45561.70833333334</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H69" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I69" t="n">
+        <v>6.11</v>
+      </c>
+      <c r="J69" t="n">
+        <v>15.8</v>
+      </c>
+      <c r="K69" t="n">
+        <v>203.69</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="n">
+        <v>45562.75</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>2649.64</v>
+      </c>
+      <c r="D70" t="n">
+        <v>2642.68</v>
+      </c>
+      <c r="E70" t="n">
+        <v>2658.72</v>
+      </c>
+      <c r="F70" s="1" t="n">
+        <v>45565.16666666666</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H70" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I70" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J70" t="n">
+        <v>9.02</v>
+      </c>
+      <c r="K70" t="n">
+        <v>212.71</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="n">
+        <v>45565.58333333334</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>2637.06</v>
+      </c>
+      <c r="D71" t="n">
+        <v>2630.09</v>
+      </c>
+      <c r="E71" t="n">
+        <v>2636.97</v>
+      </c>
+      <c r="F71" s="1" t="n">
+        <v>45565.66666666666</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H71" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I71" t="n">
+        <v>6.98</v>
+      </c>
+      <c r="J71" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K71" t="n">
+        <v>212.54</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="n">
+        <v>45569.66666666666</v>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>2638.92</v>
+      </c>
+      <c r="D72" t="n">
+        <v>2633.17</v>
+      </c>
+      <c r="E72" t="n">
+        <v>2649.15</v>
+      </c>
+      <c r="F72" s="1" t="n">
+        <v>45569.70833333334</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H72" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I72" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J72" t="n">
+        <v>10.16</v>
+      </c>
+      <c r="K72" t="n">
+        <v>222.7</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="1" t="n">
+        <v>45573.75</v>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>2621.26</v>
+      </c>
+      <c r="D73" t="n">
+        <v>2611.48</v>
+      </c>
+      <c r="E73" t="n">
+        <v>2611.26</v>
+      </c>
+      <c r="F73" s="1" t="n">
+        <v>45573.75</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H73" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I73" t="n">
+        <v>9.77</v>
+      </c>
+      <c r="J73" t="n">
+        <v>-10.07</v>
+      </c>
+      <c r="K73" t="n">
+        <v>212.63</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="n">
+        <v>45573.83333333334</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>2609.28</v>
+      </c>
+      <c r="D74" t="n">
+        <v>2599.41</v>
+      </c>
+      <c r="E74" t="n">
+        <v>2614.25</v>
+      </c>
+      <c r="F74" s="1" t="n">
+        <v>45574.375</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H74" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I74" t="n">
+        <v>9.869999999999999</v>
+      </c>
+      <c r="J74" t="n">
+        <v>4.91</v>
+      </c>
+      <c r="K74" t="n">
+        <v>217.54</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="n">
+        <v>45576.25</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2642.08</v>
+      </c>
+      <c r="D75" t="n">
+        <v>2649.38</v>
+      </c>
+      <c r="E75" t="n">
+        <v>2649.6</v>
+      </c>
+      <c r="F75" s="1" t="n">
+        <v>45576.625</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H75" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I75" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J75" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="K75" t="n">
+        <v>209.94</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="n">
+        <v>45581.41666666666</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>2676.94</v>
+      </c>
+      <c r="D76" t="n">
+        <v>2683.9</v>
+      </c>
+      <c r="E76" t="n">
+        <v>2684.12</v>
+      </c>
+      <c r="F76" s="1" t="n">
+        <v>45581.66666666666</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H76" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I76" t="n">
+        <v>6.95</v>
+      </c>
+      <c r="J76" t="n">
+        <v>-7.25</v>
+      </c>
+      <c r="K76" t="n">
+        <v>202.69</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="1" t="n">
+        <v>45582.20833333334</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>2682.86</v>
+      </c>
+      <c r="D77" t="n">
+        <v>2690.99</v>
+      </c>
+      <c r="E77" t="n">
+        <v>2682.96</v>
+      </c>
+      <c r="F77" s="1" t="n">
+        <v>45582.33333333334</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H77" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I77" t="n">
+        <v>8.130000000000001</v>
+      </c>
+      <c r="J77" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K77" t="n">
+        <v>202.52</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="n">
+        <v>45582.58333333334</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>2687.24</v>
+      </c>
+      <c r="D78" t="n">
+        <v>2694.46</v>
+      </c>
+      <c r="E78" t="n">
+        <v>2684.21</v>
+      </c>
+      <c r="F78" s="1" t="n">
+        <v>45582.66666666666</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H78" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I78" t="n">
+        <v>7.22</v>
+      </c>
+      <c r="J78" t="n">
+        <v>2.96</v>
+      </c>
+      <c r="K78" t="n">
+        <v>205.48</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="1" t="n">
+        <v>45583.20833333334</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>2704.3</v>
+      </c>
+      <c r="D79" t="n">
+        <v>2714.16</v>
+      </c>
+      <c r="E79" t="n">
+        <v>2714.39</v>
+      </c>
+      <c r="F79" s="1" t="n">
+        <v>45583.625</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H79" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I79" t="n">
+        <v>9.859999999999999</v>
+      </c>
+      <c r="J79" t="n">
+        <v>-10.15</v>
+      </c>
+      <c r="K79" t="n">
+        <v>195.33</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="1" t="n">
+        <v>45590.25</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>2728.56</v>
+      </c>
+      <c r="D80" t="n">
+        <v>2719.95</v>
+      </c>
+      <c r="E80" t="n">
+        <v>2719.73</v>
+      </c>
+      <c r="F80" s="1" t="n">
+        <v>45590.45833333334</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H80" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I80" t="n">
+        <v>8.609999999999999</v>
+      </c>
+      <c r="J80" t="n">
+        <v>-8.91</v>
+      </c>
+      <c r="K80" t="n">
+        <v>186.42</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="n">
+        <v>45594.16666666666</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>2751.88</v>
+      </c>
+      <c r="D81" t="n">
+        <v>2758.71</v>
+      </c>
+      <c r="E81" t="n">
+        <v>2758.94</v>
+      </c>
+      <c r="F81" s="1" t="n">
+        <v>45594.625</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H81" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I81" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="J81" t="n">
+        <v>-7.13</v>
+      </c>
+      <c r="K81" t="n">
+        <v>179.29</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="n">
+        <v>45596.625</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>2773.84</v>
+      </c>
+      <c r="D82" t="n">
+        <v>2765.88</v>
+      </c>
+      <c r="E82" t="n">
+        <v>2765.66</v>
+      </c>
+      <c r="F82" s="1" t="n">
+        <v>45596.625</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H82" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I82" t="n">
+        <v>7.95</v>
+      </c>
+      <c r="J82" t="n">
+        <v>-8.25</v>
+      </c>
+      <c r="K82" t="n">
+        <v>171.04</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="n">
+        <v>45601.20833333334</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>2728.62</v>
+      </c>
+      <c r="D83" t="n">
+        <v>2720.86</v>
+      </c>
+      <c r="E83" t="n">
+        <v>2749.08</v>
+      </c>
+      <c r="F83" s="1" t="n">
+        <v>45601.66666666666</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="H83" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I83" t="n">
+        <v>7.76</v>
+      </c>
+      <c r="J83" t="n">
+        <v>20.39</v>
+      </c>
+      <c r="K83" t="n">
+        <v>191.43</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="n">
+        <v>45610.16666666666</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>2562.7</v>
+      </c>
+      <c r="D84" t="n">
+        <v>2553.31</v>
+      </c>
+      <c r="E84" t="n">
+        <v>2553.09</v>
+      </c>
+      <c r="F84" s="1" t="n">
+        <v>45610.33333333334</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H84" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I84" t="n">
+        <v>9.390000000000001</v>
+      </c>
+      <c r="J84" t="n">
+        <v>-9.69</v>
+      </c>
+      <c r="K84" t="n">
+        <v>181.75</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="n">
+        <v>45610.5</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>2543.76</v>
+      </c>
+      <c r="D85" t="n">
+        <v>2535.45</v>
+      </c>
+      <c r="E85" t="n">
+        <v>2576.76</v>
+      </c>
+      <c r="F85" s="1" t="n">
+        <v>45610.75</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="H85" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I85" t="n">
+        <v>8.31</v>
+      </c>
+      <c r="J85" t="n">
+        <v>32.93</v>
+      </c>
+      <c r="K85" t="n">
+        <v>214.68</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="n">
+        <v>45610.91666666666</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>2575.72</v>
+      </c>
+      <c r="D86" t="n">
+        <v>2585.31</v>
+      </c>
+      <c r="E86" t="n">
+        <v>2564.4</v>
+      </c>
+      <c r="F86" s="1" t="n">
+        <v>45611.375</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H86" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I86" t="n">
+        <v>9.59</v>
+      </c>
+      <c r="J86" t="n">
+        <v>11.25</v>
+      </c>
+      <c r="K86" t="n">
+        <v>225.92</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="n">
+        <v>45611.70833333334</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>2572.66</v>
+      </c>
+      <c r="D87" t="n">
+        <v>2579.87</v>
+      </c>
+      <c r="E87" t="n">
+        <v>2572.54</v>
+      </c>
+      <c r="F87" s="1" t="n">
+        <v>45611.75</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H87" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I87" t="n">
+        <v>7.21</v>
+      </c>
+      <c r="J87" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="K87" t="n">
+        <v>225.97</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="n">
+        <v>45614.125</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>2576.34</v>
+      </c>
+      <c r="D88" t="n">
+        <v>2584.35</v>
+      </c>
+      <c r="E88" t="n">
+        <v>2584.58</v>
+      </c>
+      <c r="F88" s="1" t="n">
+        <v>45614.125</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H88" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I88" t="n">
+        <v>8.02</v>
+      </c>
+      <c r="J88" t="n">
+        <v>-8.31</v>
+      </c>
+      <c r="K88" t="n">
+        <v>217.66</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="n">
+        <v>45614.20833333334</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>2590.88</v>
+      </c>
+      <c r="D89" t="n">
+        <v>2599.95</v>
+      </c>
+      <c r="E89" t="n">
+        <v>2589.71</v>
+      </c>
+      <c r="F89" s="1" t="n">
+        <v>45614.41666666666</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H89" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I89" t="n">
+        <v>9.07</v>
+      </c>
+      <c r="J89" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K89" t="n">
+        <v>218.76</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="n">
+        <v>45614.5</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>2595.56</v>
+      </c>
+      <c r="D90" t="n">
+        <v>2603.45</v>
+      </c>
+      <c r="E90" t="n">
+        <v>2603.68</v>
+      </c>
+      <c r="F90" s="1" t="n">
+        <v>45614.625</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H90" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I90" t="n">
+        <v>7.9</v>
+      </c>
+      <c r="J90" t="n">
+        <v>-8.19</v>
+      </c>
+      <c r="K90" t="n">
+        <v>210.57</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="n">
+        <v>45614.70833333334</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>2608.22</v>
+      </c>
+      <c r="D91" t="n">
+        <v>2616.57</v>
+      </c>
+      <c r="E91" t="n">
+        <v>2616.8</v>
+      </c>
+      <c r="F91" s="1" t="n">
+        <v>45615.125</v>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H91" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I91" t="n">
+        <v>8.35</v>
+      </c>
+      <c r="J91" t="n">
+        <v>-8.640000000000001</v>
+      </c>
+      <c r="K91" t="n">
+        <v>201.92</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="n">
+        <v>45615.20833333334</v>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>2622.22</v>
+      </c>
+      <c r="D92" t="n">
+        <v>2627.81</v>
+      </c>
+      <c r="E92" t="n">
+        <v>2628.04</v>
+      </c>
+      <c r="F92" s="1" t="n">
+        <v>45615.45833333334</v>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H92" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I92" t="n">
+        <v>5.6</v>
+      </c>
+      <c r="J92" t="n">
+        <v>-5.89</v>
+      </c>
+      <c r="K92" t="n">
+        <v>196.03</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="n">
+        <v>45615.54166666666</v>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>2634.82</v>
+      </c>
+      <c r="D93" t="n">
+        <v>2640.06</v>
+      </c>
+      <c r="E93" t="n">
+        <v>2634.52</v>
+      </c>
+      <c r="F93" s="1" t="n">
+        <v>45615.58333333334</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H93" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I93" t="n">
+        <v>5.23</v>
+      </c>
+      <c r="J93" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="K93" t="n">
+        <v>196.27</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="n">
+        <v>45616.125</v>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>2637.66</v>
+      </c>
+      <c r="D94" t="n">
+        <v>2644.19</v>
+      </c>
+      <c r="E94" t="n">
+        <v>2625.66</v>
+      </c>
+      <c r="F94" s="1" t="n">
+        <v>45616.45833333334</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H94" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I94" t="n">
+        <v>6.52</v>
+      </c>
+      <c r="J94" t="n">
+        <v>11.94</v>
+      </c>
+      <c r="K94" t="n">
+        <v>208.21</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="n">
+        <v>45616.70833333334</v>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>2642.92</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2648.98</v>
+      </c>
+      <c r="E95" t="n">
+        <v>2649.21</v>
+      </c>
+      <c r="F95" s="1" t="n">
+        <v>45616.75</v>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H95" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I95" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="J95" t="n">
+        <v>-6.35</v>
+      </c>
+      <c r="K95" t="n">
+        <v>201.86</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="n">
+        <v>45616.83333333334</v>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>2651.68</v>
+      </c>
+      <c r="D96" t="n">
+        <v>2658.18</v>
+      </c>
+      <c r="E96" t="n">
+        <v>2658.41</v>
+      </c>
+      <c r="F96" s="1" t="n">
+        <v>45617.08333333334</v>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H96" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I96" t="n">
+        <v>6.5</v>
+      </c>
+      <c r="J96" t="n">
+        <v>-6.79</v>
+      </c>
+      <c r="K96" t="n">
+        <v>195.06</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="n">
+        <v>45617.45833333334</v>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>2668.58</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2673.85</v>
+      </c>
+      <c r="E97" t="n">
+        <v>2665.95</v>
+      </c>
+      <c r="F97" s="1" t="n">
+        <v>45617.66666666666</v>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H97" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I97" t="n">
+        <v>5.26</v>
+      </c>
+      <c r="J97" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="K97" t="n">
+        <v>197.63</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="n">
+        <v>45618.16666666666</v>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>2677.52</v>
+      </c>
+      <c r="D98" t="n">
+        <v>2683.66</v>
+      </c>
+      <c r="E98" t="n">
+        <v>2683.89</v>
+      </c>
+      <c r="F98" s="1" t="n">
+        <v>45618.16666666666</v>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H98" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I98" t="n">
+        <v>6.15</v>
+      </c>
+      <c r="J98" t="n">
+        <v>-6.44</v>
+      </c>
+      <c r="K98" t="n">
+        <v>191.19</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="n">
+        <v>45618.25</v>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>2686</v>
+      </c>
+      <c r="D99" t="n">
+        <v>2692.46</v>
+      </c>
+      <c r="E99" t="n">
+        <v>2692.68</v>
+      </c>
+      <c r="F99" s="1" t="n">
+        <v>45618.33333333334</v>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H99" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I99" t="n">
+        <v>6.45</v>
+      </c>
+      <c r="J99" t="n">
+        <v>-6.75</v>
+      </c>
+      <c r="K99" t="n">
+        <v>184.44</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="n">
+        <v>45618.41666666666</v>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>2696.04</v>
+      </c>
+      <c r="D100" t="n">
+        <v>2702.45</v>
+      </c>
+      <c r="E100" t="n">
+        <v>2702.68</v>
+      </c>
+      <c r="F100" s="1" t="n">
+        <v>45618.45833333334</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H100" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I100" t="n">
+        <v>6.41</v>
+      </c>
+      <c r="J100" t="n">
+        <v>-6.7</v>
+      </c>
+      <c r="K100" t="n">
+        <v>177.74</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="n">
+        <v>45618.54166666666</v>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>2707.52</v>
+      </c>
+      <c r="D101" t="n">
+        <v>2714.26</v>
+      </c>
+      <c r="E101" t="n">
+        <v>2704.04</v>
+      </c>
+      <c r="F101" s="1" t="n">
+        <v>45618.58333333334</v>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H101" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I101" t="n">
+        <v>6.75</v>
+      </c>
+      <c r="J101" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="K101" t="n">
+        <v>181.14</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="n">
+        <v>45621.04166666666</v>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>2692.02</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2700.26</v>
+      </c>
+      <c r="E102" t="n">
+        <v>2700.48</v>
+      </c>
+      <c r="F102" s="1" t="n">
+        <v>45621.04166666666</v>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H102" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I102" t="n">
+        <v>8.23</v>
+      </c>
+      <c r="J102" t="n">
+        <v>-8.529999999999999</v>
+      </c>
+      <c r="K102" t="n">
+        <v>172.61</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="n">
+        <v>45623.20833333334</v>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>2637.36</v>
+      </c>
+      <c r="D103" t="n">
+        <v>2644.97</v>
+      </c>
+      <c r="E103" t="n">
+        <v>2645.19</v>
+      </c>
+      <c r="F103" s="1" t="n">
+        <v>45623.29166666666</v>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H103" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I103" t="n">
+        <v>7.6</v>
+      </c>
+      <c r="J103" t="n">
+        <v>-7.9</v>
+      </c>
+      <c r="K103" t="n">
+        <v>164.71</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="n">
+        <v>45623.375</v>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>2647.48</v>
+      </c>
+      <c r="D104" t="n">
+        <v>2653.04</v>
+      </c>
+      <c r="E104" t="n">
+        <v>2653.26</v>
+      </c>
+      <c r="F104" s="1" t="n">
+        <v>45623.41666666666</v>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H104" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I104" t="n">
+        <v>5.55</v>
+      </c>
+      <c r="J104" t="n">
+        <v>-5.85</v>
+      </c>
+      <c r="K104" t="n">
+        <v>158.87</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="n">
+        <v>45623.5</v>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>2648.1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>2653.84</v>
+      </c>
+      <c r="E105" t="n">
+        <v>2654.07</v>
+      </c>
+      <c r="F105" s="1" t="n">
+        <v>45623.58333333334</v>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H105" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I105" t="n">
+        <v>5.75</v>
+      </c>
+      <c r="J105" t="n">
+        <v>-6.04</v>
+      </c>
+      <c r="K105" t="n">
+        <v>152.82</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="n">
+        <v>45623.66666666666</v>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>2655.96</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2662.45</v>
+      </c>
+      <c r="E106" t="n">
+        <v>2642.23</v>
+      </c>
+      <c r="F106" s="1" t="n">
+        <v>45623.75</v>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H106" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I106" t="n">
+        <v>6.48</v>
+      </c>
+      <c r="J106" t="n">
+        <v>13.67</v>
+      </c>
+      <c r="K106" t="n">
+        <v>166.49</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="n">
+        <v>45624.16666666666</v>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>2629.04</v>
+      </c>
+      <c r="D107" t="n">
+        <v>2621.78</v>
+      </c>
+      <c r="E107" t="n">
+        <v>2642.08</v>
+      </c>
+      <c r="F107" s="1" t="n">
+        <v>45624.66666666666</v>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H107" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I107" t="n">
+        <v>7.27</v>
+      </c>
+      <c r="J107" t="n">
+        <v>12.96</v>
+      </c>
+      <c r="K107" t="n">
+        <v>179.45</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="n">
+        <v>45625.20833333334</v>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>2657.2</v>
+      </c>
+      <c r="D108" t="n">
+        <v>2662.99</v>
+      </c>
+      <c r="E108" t="n">
+        <v>2663.22</v>
+      </c>
+      <c r="F108" s="1" t="n">
+        <v>45625.25</v>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H108" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I108" t="n">
+        <v>5.79</v>
+      </c>
+      <c r="J108" t="n">
+        <v>-6.09</v>
+      </c>
+      <c r="K108" t="n">
+        <v>173.36</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="n">
+        <v>45625.33333333334</v>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>2662.08</v>
+      </c>
+      <c r="D109" t="n">
+        <v>2668.13</v>
+      </c>
+      <c r="E109" t="n">
+        <v>2660.84</v>
+      </c>
+      <c r="F109" s="1" t="n">
+        <v>45625.45833333334</v>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H109" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I109" t="n">
+        <v>6.06</v>
+      </c>
+      <c r="J109" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="K109" t="n">
+        <v>174.52</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="n">
+        <v>45628.08333333334</v>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>2646.14</v>
+      </c>
+      <c r="D110" t="n">
+        <v>2639.22</v>
+      </c>
+      <c r="E110" t="n">
+        <v>2638.99</v>
+      </c>
+      <c r="F110" s="1" t="n">
+        <v>45628.08333333334</v>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H110" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I110" t="n">
+        <v>6.92</v>
+      </c>
+      <c r="J110" t="n">
+        <v>-7.21</v>
+      </c>
+      <c r="K110" t="n">
+        <v>167.31</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="n">
+        <v>45628.16666666666</v>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>2636.12</v>
+      </c>
+      <c r="D111" t="n">
+        <v>2627.84</v>
+      </c>
+      <c r="E111" t="n">
+        <v>2627.62</v>
+      </c>
+      <c r="F111" s="1" t="n">
+        <v>45628.16666666666</v>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H111" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I111" t="n">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="J111" t="n">
+        <v>-8.58</v>
+      </c>
+      <c r="K111" t="n">
+        <v>158.73</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="n">
+        <v>45629.375</v>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>2646.6</v>
+      </c>
+      <c r="D112" t="n">
+        <v>2652.09</v>
+      </c>
+      <c r="E112" t="n">
+        <v>2644.99</v>
+      </c>
+      <c r="F112" s="1" t="n">
+        <v>45629.45833333334</v>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H112" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I112" t="n">
+        <v>5.49</v>
+      </c>
+      <c r="J112" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="K112" t="n">
+        <v>160.27</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="n">
+        <v>45629.66666666666</v>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>2652.72</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2658.66</v>
+      </c>
+      <c r="E113" t="n">
+        <v>2641.38</v>
+      </c>
+      <c r="F113" s="1" t="n">
+        <v>45629.75</v>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H113" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I113" t="n">
+        <v>5.94</v>
+      </c>
+      <c r="J113" t="n">
+        <v>11.26</v>
+      </c>
+      <c r="K113" t="n">
+        <v>171.53</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="n">
+        <v>45630.33333333334</v>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>2649.56</v>
+      </c>
+      <c r="D114" t="n">
+        <v>2654.9</v>
+      </c>
+      <c r="E114" t="n">
+        <v>2642.23</v>
+      </c>
+      <c r="F114" s="1" t="n">
+        <v>45630.45833333334</v>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H114" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I114" t="n">
+        <v>5.35</v>
+      </c>
+      <c r="J114" t="n">
+        <v>7.25</v>
+      </c>
+      <c r="K114" t="n">
+        <v>178.78</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="n">
+        <v>45630.625</v>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>2636.88</v>
+      </c>
+      <c r="D115" t="n">
+        <v>2631.7</v>
+      </c>
+      <c r="E115" t="n">
+        <v>2648.07</v>
+      </c>
+      <c r="F115" s="1" t="n">
+        <v>45630.70833333334</v>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H115" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I115" t="n">
+        <v>5.17</v>
+      </c>
+      <c r="J115" t="n">
+        <v>11.13</v>
+      </c>
+      <c r="K115" t="n">
+        <v>189.91</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="n">
+        <v>45631.625</v>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>2653.02</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2658.39</v>
+      </c>
+      <c r="E116" t="n">
+        <v>2649.94</v>
+      </c>
+      <c r="F116" s="1" t="n">
+        <v>45631.66666666666</v>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H116" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I116" t="n">
+        <v>5.38</v>
+      </c>
+      <c r="J116" t="n">
+        <v>3</v>
+      </c>
+      <c r="K116" t="n">
+        <v>192.91</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="n">
+        <v>45631.75</v>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>2640.46</v>
+      </c>
+      <c r="D117" t="n">
+        <v>2633.67</v>
+      </c>
+      <c r="E117" t="n">
+        <v>2633.44</v>
+      </c>
+      <c r="F117" s="1" t="n">
+        <v>45631.75</v>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H117" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I117" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="J117" t="n">
+        <v>-7.08</v>
+      </c>
+      <c r="K117" t="n">
+        <v>185.83</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="n">
+        <v>45631.83333333334</v>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>2628.2</v>
+      </c>
+      <c r="D118" t="n">
+        <v>2620.44</v>
+      </c>
+      <c r="E118" t="n">
+        <v>2620.21</v>
+      </c>
+      <c r="F118" s="1" t="n">
+        <v>45632.125</v>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H118" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I118" t="n">
+        <v>7.77</v>
+      </c>
+      <c r="J118" t="n">
+        <v>-8.06</v>
+      </c>
+      <c r="K118" t="n">
+        <v>177.76</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="n">
+        <v>45635.125</v>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>2631.22</v>
+      </c>
+      <c r="D119" t="n">
+        <v>2623.2</v>
+      </c>
+      <c r="E119" t="n">
+        <v>2642.24</v>
+      </c>
+      <c r="F119" s="1" t="n">
+        <v>45635.16666666666</v>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H119" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I119" t="n">
+        <v>8.029999999999999</v>
+      </c>
+      <c r="J119" t="n">
+        <v>10.94</v>
+      </c>
+      <c r="K119" t="n">
+        <v>188.71</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="n">
+        <v>45635.41666666666</v>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>2650.54</v>
+      </c>
+      <c r="D120" t="n">
+        <v>2658.41</v>
+      </c>
+      <c r="E120" t="n">
+        <v>2658.64</v>
+      </c>
+      <c r="F120" s="1" t="n">
+        <v>45635.54166666666</v>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H120" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I120" t="n">
+        <v>7.88</v>
+      </c>
+      <c r="J120" t="n">
+        <v>-8.17</v>
+      </c>
+      <c r="K120" t="n">
+        <v>180.53</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="n">
+        <v>45635.625</v>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>2655.96</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2664.34</v>
+      </c>
+      <c r="E121" t="n">
+        <v>2664.57</v>
+      </c>
+      <c r="F121" s="1" t="n">
+        <v>45635.625</v>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H121" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I121" t="n">
+        <v>8.390000000000001</v>
+      </c>
+      <c r="J121" t="n">
+        <v>-8.68</v>
+      </c>
+      <c r="K121" t="n">
+        <v>171.85</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="n">
+        <v>45635.70833333334</v>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>2673.8</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2681.9</v>
+      </c>
+      <c r="E122" t="n">
+        <v>2665.01</v>
+      </c>
+      <c r="F122" s="1" t="n">
+        <v>45636.08333333334</v>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H122" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I122" t="n">
+        <v>8.109999999999999</v>
+      </c>
+      <c r="J122" t="n">
+        <v>8.710000000000001</v>
+      </c>
+      <c r="K122" t="n">
+        <v>180.57</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="n">
+        <v>45636.54166666666</v>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>2675.26</v>
+      </c>
+      <c r="D123" t="n">
+        <v>2680.8</v>
+      </c>
+      <c r="E123" t="n">
+        <v>2681.03</v>
+      </c>
+      <c r="F123" s="1" t="n">
+        <v>45636.625</v>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H123" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I123" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="J123" t="n">
+        <v>-5.83</v>
+      </c>
+      <c r="K123" t="n">
+        <v>174.73</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="n">
+        <v>45636.70833333334</v>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>2688.84</v>
+      </c>
+      <c r="D124" t="n">
+        <v>2695.63</v>
+      </c>
+      <c r="E124" t="n">
+        <v>2695.85</v>
+      </c>
+      <c r="F124" s="1" t="n">
+        <v>45637.04166666666</v>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H124" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I124" t="n">
+        <v>6.79</v>
+      </c>
+      <c r="J124" t="n">
+        <v>-7.09</v>
+      </c>
+      <c r="K124" t="n">
+        <v>167.64</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="n">
+        <v>45637.125</v>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>2700.84</v>
+      </c>
+      <c r="D125" t="n">
+        <v>2707.27</v>
+      </c>
+      <c r="E125" t="n">
+        <v>2688.96</v>
+      </c>
+      <c r="F125" s="1" t="n">
+        <v>45637.29166666666</v>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H125" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I125" t="n">
+        <v>6.44</v>
+      </c>
+      <c r="J125" t="n">
+        <v>11.8</v>
+      </c>
+      <c r="K125" t="n">
+        <v>179.45</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="n">
+        <v>45637.875</v>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>2713.7</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2722.66</v>
+      </c>
+      <c r="E126" t="n">
+        <v>2722.89</v>
+      </c>
+      <c r="F126" s="1" t="n">
+        <v>45638.08333333334</v>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H126" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I126" t="n">
+        <v>8.970000000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>-9.26</v>
+      </c>
+      <c r="K126" t="n">
+        <v>170.18</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="n">
+        <v>45638.625</v>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>2706.76</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2699.46</v>
+      </c>
+      <c r="E127" t="n">
+        <v>2699.24</v>
+      </c>
+      <c r="F127" s="1" t="n">
+        <v>45638.625</v>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H127" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I127" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="J127" t="n">
+        <v>-7.6</v>
+      </c>
+      <c r="K127" t="n">
+        <v>162.58</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="n">
+        <v>45643.5</v>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>2639.78</v>
+      </c>
+      <c r="D128" t="n">
+        <v>2631.82</v>
+      </c>
+      <c r="E128" t="n">
+        <v>2639.68</v>
+      </c>
+      <c r="F128" s="1" t="n">
+        <v>45644.66666666666</v>
+      </c>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H128" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I128" t="n">
+        <v>7.96</v>
+      </c>
+      <c r="J128" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K128" t="n">
+        <v>162.41</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="n">
+        <v>45652.75</v>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>2636.38</v>
+      </c>
+      <c r="D129" t="n">
+        <v>2643</v>
+      </c>
+      <c r="E129" t="n">
+        <v>2636.48</v>
+      </c>
+      <c r="F129" s="1" t="n">
+        <v>45653.33333333334</v>
+      </c>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H129" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I129" t="n">
+        <v>6.63</v>
+      </c>
+      <c r="J129" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K129" t="n">
+        <v>162.24</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="n">
+        <v>45664.66666666666</v>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2662.3</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2669.74</v>
+      </c>
+      <c r="E130" t="n">
+        <v>2642.71</v>
+      </c>
+      <c r="F130" s="1" t="n">
+        <v>45664.70833333334</v>
+      </c>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>TP</t>
+        </is>
+      </c>
+      <c r="H130" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I130" t="n">
+        <v>7.43</v>
+      </c>
+      <c r="J130" t="n">
+        <v>19.52</v>
+      </c>
+      <c r="K130" t="n">
+        <v>181.77</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="n">
+        <v>45665.79166666666</v>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>2669.4</v>
+      </c>
+      <c r="D131" t="n">
+        <v>2677.06</v>
+      </c>
+      <c r="E131" t="n">
+        <v>2661.24</v>
+      </c>
+      <c r="F131" s="1" t="n">
+        <v>45665.91666666666</v>
+      </c>
+      <c r="G131" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H131" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I131" t="n">
+        <v>7.67</v>
+      </c>
+      <c r="J131" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="K131" t="n">
+        <v>189.85</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="n">
+        <v>45672.66666666666</v>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>2693.86</v>
+      </c>
+      <c r="D132" t="n">
+        <v>2700.96</v>
+      </c>
+      <c r="E132" t="n">
+        <v>2687.65</v>
+      </c>
+      <c r="F132" s="1" t="n">
+        <v>45672.75</v>
+      </c>
+      <c r="G132" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H132" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I132" t="n">
+        <v>7.09</v>
+      </c>
+      <c r="J132" t="n">
+        <v>6.14</v>
+      </c>
+      <c r="K132" t="n">
+        <v>195.99</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="n">
+        <v>45681.25</v>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>2772</v>
+      </c>
+      <c r="D133" t="n">
+        <v>2781.7</v>
+      </c>
+      <c r="E133" t="n">
+        <v>2781.93</v>
+      </c>
+      <c r="F133" s="1" t="n">
+        <v>45681.625</v>
+      </c>
+      <c r="G133" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H133" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I133" t="n">
+        <v>9.699999999999999</v>
+      </c>
+      <c r="J133" t="n">
+        <v>-9.99</v>
+      </c>
+      <c r="K133" t="n">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="n">
+        <v>45687.45833333334</v>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>2776.28</v>
+      </c>
+      <c r="D134" t="n">
+        <v>2783.8</v>
+      </c>
+      <c r="E134" t="n">
+        <v>2784.03</v>
+      </c>
+      <c r="F134" s="1" t="n">
+        <v>45687.625</v>
+      </c>
+      <c r="G134" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H134" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I134" t="n">
+        <v>7.53</v>
+      </c>
+      <c r="J134" t="n">
+        <v>-7.82</v>
+      </c>
+      <c r="K134" t="n">
+        <v>178.18</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="n">
+        <v>45687.70833333334</v>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>2787.76</v>
+      </c>
+      <c r="D135" t="n">
+        <v>2795.08</v>
+      </c>
+      <c r="E135" t="n">
+        <v>2795.3</v>
+      </c>
+      <c r="F135" s="1" t="n">
+        <v>45687.70833333334</v>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H135" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I135" t="n">
+        <v>7.31</v>
+      </c>
+      <c r="J135" t="n">
+        <v>-7.61</v>
+      </c>
+      <c r="K135" t="n">
+        <v>170.57</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="n">
+        <v>45708.54166666666</v>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>2952.14</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2960.58</v>
+      </c>
+      <c r="E136" t="n">
+        <v>2947.69</v>
+      </c>
+      <c r="F136" s="1" t="n">
+        <v>45708.625</v>
+      </c>
+      <c r="G136" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H136" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I136" t="n">
+        <v>8.449999999999999</v>
+      </c>
+      <c r="J136" t="n">
+        <v>4.37</v>
+      </c>
+      <c r="K136" t="n">
+        <v>174.94</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="n">
+        <v>45729.29166666666</v>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>2944.42</v>
+      </c>
+      <c r="D137" t="n">
+        <v>2952.6</v>
+      </c>
+      <c r="E137" t="n">
+        <v>2941.31</v>
+      </c>
+      <c r="F137" s="1" t="n">
+        <v>45729.41666666666</v>
+      </c>
+      <c r="G137" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H137" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I137" t="n">
+        <v>8.19</v>
+      </c>
+      <c r="J137" t="n">
+        <v>3.03</v>
+      </c>
+      <c r="K137" t="n">
+        <v>177.97</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="n">
+        <v>45733.54166666666</v>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>2998.68</v>
+      </c>
+      <c r="D138" t="n">
+        <v>3004.23</v>
+      </c>
+      <c r="E138" t="n">
+        <v>2993.23</v>
+      </c>
+      <c r="F138" s="1" t="n">
+        <v>45733.66666666666</v>
+      </c>
+      <c r="G138" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H138" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I138" t="n">
+        <v>5.54</v>
+      </c>
+      <c r="J138" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="K138" t="n">
+        <v>183.36</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="n">
+        <v>45734.20833333334</v>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>3010.6</v>
+      </c>
+      <c r="D139" t="n">
+        <v>3016.58</v>
+      </c>
+      <c r="E139" t="n">
+        <v>3016.8</v>
+      </c>
+      <c r="F139" s="1" t="n">
+        <v>45734.25</v>
+      </c>
+      <c r="G139" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H139" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I139" t="n">
+        <v>5.98</v>
+      </c>
+      <c r="J139" t="n">
+        <v>-6.28</v>
+      </c>
+      <c r="K139" t="n">
+        <v>177.09</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="n">
+        <v>45734.45833333334</v>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>3026.32</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3031.9</v>
+      </c>
+      <c r="E140" t="n">
+        <v>3026.42</v>
+      </c>
+      <c r="F140" s="1" t="n">
+        <v>45734.54166666666</v>
+      </c>
+      <c r="G140" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H140" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I140" t="n">
+        <v>5.57</v>
+      </c>
+      <c r="J140" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K140" t="n">
+        <v>176.92</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="n">
+        <v>45737.66666666666</v>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>BUY</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>3006.74</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2998.93</v>
+      </c>
+      <c r="E141" t="n">
+        <v>3014.32</v>
+      </c>
+      <c r="F141" s="1" t="n">
+        <v>45740.16666666666</v>
+      </c>
+      <c r="G141" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H141" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I141" t="n">
+        <v>7.81</v>
+      </c>
+      <c r="J141" t="n">
+        <v>7.5</v>
+      </c>
+      <c r="K141" t="n">
+        <v>184.42</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="n">
+        <v>45743.25</v>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>3033.34</v>
+      </c>
+      <c r="D142" t="n">
+        <v>3038.67</v>
+      </c>
+      <c r="E142" t="n">
+        <v>3033.44</v>
+      </c>
+      <c r="F142" s="1" t="n">
+        <v>45743.375</v>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H142" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I142" t="n">
+        <v>5.33</v>
+      </c>
+      <c r="J142" t="n">
+        <v>-0.17</v>
+      </c>
+      <c r="K142" t="n">
+        <v>184.25</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="n">
+        <v>45743.5</v>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>3039.68</v>
+      </c>
+      <c r="D143" t="n">
+        <v>3045.16</v>
+      </c>
+      <c r="E143" t="n">
+        <v>3045.38</v>
+      </c>
+      <c r="F143" s="1" t="n">
+        <v>45743.5</v>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H143" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I143" t="n">
+        <v>5.48</v>
+      </c>
+      <c r="J143" t="n">
+        <v>-5.77</v>
+      </c>
+      <c r="K143" t="n">
+        <v>178.47</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="n">
+        <v>45743.58333333334</v>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>3054.34</v>
+      </c>
+      <c r="D144" t="n">
+        <v>3060.89</v>
+      </c>
+      <c r="E144" t="n">
+        <v>3043.39</v>
+      </c>
+      <c r="F144" s="1" t="n">
+        <v>45743.66666666666</v>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>TRAIL</t>
+        </is>
+      </c>
+      <c r="H144" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I144" t="n">
+        <v>6.55</v>
+      </c>
+      <c r="J144" t="n">
+        <v>10.89</v>
+      </c>
+      <c r="K144" t="n">
+        <v>189.36</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="n">
+        <v>45763.125</v>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SELL</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>3251.56</v>
+      </c>
+      <c r="D145" t="n">
+        <v>3260.7</v>
+      </c>
+      <c r="E145" t="n">
+        <v>3260.93</v>
+      </c>
+      <c r="F145" s="1" t="n">
+        <v>45763.125</v>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>SL</t>
+        </is>
+      </c>
+      <c r="H145" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="I145" t="n">
+        <v>9.140000000000001</v>
+      </c>
+      <c r="J145" t="n">
+        <v>-9.43</v>
+      </c>
+      <c r="K145" t="n">
+        <v>179.93</v>
       </c>
     </row>
   </sheetData>
@@ -1919,7 +6400,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:J11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1955,10 +6436,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>be_trigger_R</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>trail_R</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>max_hold</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_score</t>
         </is>
@@ -1966,28 +6457,322 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>44026.5</v>
+        <v>45492.5</v>
       </c>
       <c r="B2" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
         <v>14</v>
       </c>
       <c r="D2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>1</v>
+      </c>
+      <c r="I2" t="n">
+        <v>48</v>
+      </c>
+      <c r="J2" t="n">
+        <v>1391.31</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="n">
+        <v>45523.375</v>
+      </c>
+      <c r="B3" t="n">
+        <v>20</v>
+      </c>
+      <c r="C3" t="n">
+        <v>14</v>
+      </c>
+      <c r="D3" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E3" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F3" t="n">
+        <v>3</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>1</v>
+      </c>
+      <c r="I3" t="n">
+        <v>48</v>
+      </c>
+      <c r="J3" t="n">
+        <v>-999.22</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="n">
+        <v>45552.33333333334</v>
+      </c>
+      <c r="B4" t="n">
+        <v>40</v>
+      </c>
+      <c r="C4" t="n">
+        <v>14</v>
+      </c>
+      <c r="D4" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E4" t="n">
+        <v>1</v>
+      </c>
+      <c r="F4" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1</v>
+      </c>
+      <c r="I4" t="n">
+        <v>48</v>
+      </c>
+      <c r="J4" t="n">
+        <v>-138.18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n">
+        <v>45581.20833333334</v>
+      </c>
+      <c r="B5" t="n">
+        <v>20</v>
+      </c>
+      <c r="C5" t="n">
+        <v>14</v>
+      </c>
+      <c r="D5" t="n">
         <v>2</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F5" t="n">
+        <v>4</v>
+      </c>
+      <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>48</v>
+      </c>
+      <c r="J5" t="n">
+        <v>5581.95</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n">
+        <v>45610.08333333334</v>
+      </c>
+      <c r="B6" t="n">
+        <v>20</v>
+      </c>
+      <c r="C6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D6" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="E6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F6" t="n">
+        <v>4</v>
+      </c>
+      <c r="G6" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="n">
+        <v>1</v>
+      </c>
+      <c r="I6" t="n">
+        <v>48</v>
+      </c>
+      <c r="J6" t="n">
+        <v>5924.36</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="n">
+        <v>45639.125</v>
+      </c>
+      <c r="B7" t="n">
+        <v>40</v>
+      </c>
+      <c r="C7" t="n">
+        <v>14</v>
+      </c>
+      <c r="D7" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F7" t="n">
+        <v>4</v>
+      </c>
+      <c r="G7" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>48</v>
+      </c>
+      <c r="J7" t="n">
+        <v>-2452.96</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n">
+        <v>45672.20833333334</v>
+      </c>
+      <c r="B8" t="n">
+        <v>40</v>
+      </c>
+      <c r="C8" t="n">
+        <v>14</v>
+      </c>
+      <c r="D8" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F8" t="n">
+        <v>4</v>
+      </c>
+      <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>48</v>
+      </c>
+      <c r="J8" t="n">
+        <v>6569.01</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n">
+        <v>45701.16666666666</v>
+      </c>
+      <c r="B9" t="n">
+        <v>40</v>
+      </c>
+      <c r="C9" t="n">
+        <v>14</v>
+      </c>
+      <c r="D9" t="n">
         <v>2</v>
       </c>
-      <c r="F2" t="n">
+      <c r="E9" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="F9" t="n">
         <v>3</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G9" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="n">
+        <v>1</v>
+      </c>
+      <c r="I9" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="n">
-        <v>-68.62</v>
+      <c r="J9" t="n">
+        <v>3153.36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="n">
+        <v>45730.08333333334</v>
+      </c>
+      <c r="B10" t="n">
+        <v>40</v>
+      </c>
+      <c r="C10" t="n">
+        <v>14</v>
+      </c>
+      <c r="D10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E10" t="n">
+        <v>1</v>
+      </c>
+      <c r="F10" t="n">
+        <v>4</v>
+      </c>
+      <c r="G10" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>48</v>
+      </c>
+      <c r="J10" t="n">
+        <v>3895.56</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n">
+        <v>45758.95833333334</v>
+      </c>
+      <c r="B11" t="n">
+        <v>40</v>
+      </c>
+      <c r="C11" t="n">
+        <v>14</v>
+      </c>
+      <c r="D11" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="E11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F11" t="n">
+        <v>3</v>
+      </c>
+      <c r="G11" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="n">
+        <v>1</v>
+      </c>
+      <c r="I11" t="n">
+        <v>48</v>
+      </c>
+      <c r="J11" t="n">
+        <v>1836</v>
       </c>
     </row>
   </sheetData>
@@ -2001,7 +6786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J44"/>
+  <dimension ref="A1:K19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2047,10 +6832,15 @@
       </c>
       <c r="I1" t="inlineStr">
         <is>
+          <t>Risk $</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
           <t>P/L $</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>Balance $</t>
         </is>
@@ -2058,7 +6848,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45541</v>
+        <v>45926</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
@@ -2066,16 +6856,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>53849.95</v>
+        <v>109680.1</v>
       </c>
       <c r="D2" t="n">
-        <v>51970.14</v>
+        <v>108666.15</v>
       </c>
       <c r="E2" t="n">
-        <v>57598.58</v>
+        <v>113724.93</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>45545</v>
+        <v>45929</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -2083,18 +6873,21 @@
         </is>
       </c>
       <c r="H2" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I2" t="n">
-        <v>224.5</v>
+        <v>20.28</v>
       </c>
       <c r="J2" t="n">
-        <v>724.5</v>
+        <v>80.76000000000001</v>
+      </c>
+      <c r="K2" t="n">
+        <v>580.76</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45554</v>
+        <v>45932</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
@@ -2102,16 +6895,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>62983.61</v>
+        <v>120547.59</v>
       </c>
       <c r="D3" t="n">
-        <v>64782.66</v>
+        <v>122056.68</v>
       </c>
       <c r="E3" t="n">
-        <v>64793.66</v>
+        <v>122067.68</v>
       </c>
       <c r="F3" s="1" t="n">
-        <v>45561</v>
+        <v>45933</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -2119,18 +6912,21 @@
         </is>
       </c>
       <c r="H3" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I3" t="n">
-        <v>-109.02</v>
+        <v>15.09</v>
       </c>
       <c r="J3" t="n">
-        <v>615.47</v>
+        <v>-15.27</v>
+      </c>
+      <c r="K3" t="n">
+        <v>565.49</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45563</v>
+        <v>45935</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
@@ -2138,16 +6934,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>65759.53</v>
+        <v>123512.77</v>
       </c>
       <c r="D4" t="n">
-        <v>67140.37</v>
+        <v>125165.07</v>
       </c>
       <c r="E4" t="n">
-        <v>63008.84</v>
+        <v>116914.56</v>
       </c>
       <c r="F4" s="1" t="n">
-        <v>45566</v>
+        <v>45940</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -2155,18 +6951,21 @@
         </is>
       </c>
       <c r="H4" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I4" t="n">
-        <v>164.62</v>
+        <v>16.52</v>
       </c>
       <c r="J4" t="n">
-        <v>780.1</v>
+        <v>65.91</v>
+      </c>
+      <c r="K4" t="n">
+        <v>631.4</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45576</v>
+        <v>45947</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
@@ -2174,52 +6973,55 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>62473.54</v>
+        <v>106636.67</v>
       </c>
       <c r="D5" t="n">
-        <v>61347.06</v>
+        <v>104254.89</v>
       </c>
       <c r="E5" t="n">
-        <v>64715.5</v>
+        <v>110973.44</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>45579</v>
+        <v>45959</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H5" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I5" t="n">
-        <v>134.1</v>
+        <v>23.82</v>
       </c>
       <c r="J5" t="n">
-        <v>914.1900000000001</v>
+        <v>43.3</v>
+      </c>
+      <c r="K5" t="n">
+        <v>674.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="n">
-        <v>45581</v>
+        <v>45966</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>67651.95</v>
+        <v>103926.88</v>
       </c>
       <c r="D6" t="n">
-        <v>68990.00999999999</v>
+        <v>102079.14</v>
       </c>
       <c r="E6" t="n">
-        <v>69001.00999999999</v>
+        <v>102068.14</v>
       </c>
       <c r="F6" s="1" t="n">
-        <v>45585</v>
+        <v>45967</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -2227,71 +7029,77 @@
         </is>
       </c>
       <c r="H6" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I6" t="n">
-        <v>-81.36</v>
+        <v>18.48</v>
       </c>
       <c r="J6" t="n">
-        <v>832.83</v>
+        <v>-18.66</v>
+      </c>
+      <c r="K6" t="n">
+        <v>656.04</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="n">
-        <v>45595</v>
+        <v>45976</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>72439.28</v>
+        <v>95552.32000000001</v>
       </c>
       <c r="D7" t="n">
-        <v>74038.84</v>
+        <v>93143.56</v>
       </c>
       <c r="E7" t="n">
-        <v>69251.16</v>
+        <v>93132.56</v>
       </c>
       <c r="F7" s="1" t="n">
-        <v>45599</v>
+        <v>45978</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H7" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I7" t="n">
-        <v>190.87</v>
+        <v>24.09</v>
       </c>
       <c r="J7" t="n">
-        <v>1023.7</v>
+        <v>-24.27</v>
+      </c>
+      <c r="K7" t="n">
+        <v>631.77</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="n">
-        <v>45603</v>
+        <v>45981</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>75961.3</v>
+        <v>86922.3</v>
       </c>
       <c r="D8" t="n">
-        <v>78381.34</v>
+        <v>84894.33</v>
       </c>
       <c r="E8" t="n">
-        <v>78392.34</v>
+        <v>84883.33</v>
       </c>
       <c r="F8" s="1" t="n">
-        <v>45606</v>
+        <v>45983</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -2299,35 +7107,38 @@
         </is>
       </c>
       <c r="H8" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I8" t="n">
-        <v>-146.28</v>
+        <v>20.28</v>
       </c>
       <c r="J8" t="n">
-        <v>877.41</v>
+        <v>-20.46</v>
+      </c>
+      <c r="K8" t="n">
+        <v>611.3099999999999</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n">
-        <v>45608</v>
+        <v>46007</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>88037.75</v>
+        <v>87763.42999999999</v>
       </c>
       <c r="D9" t="n">
-        <v>91123.13</v>
+        <v>86143.35000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>91134.13</v>
+        <v>86132.35000000001</v>
       </c>
       <c r="F9" s="1" t="n">
-        <v>45611</v>
+        <v>46008</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -2335,54 +7146,60 @@
         </is>
       </c>
       <c r="H9" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I9" t="n">
-        <v>-186.2</v>
+        <v>16.2</v>
       </c>
       <c r="J9" t="n">
-        <v>691.21</v>
+        <v>-16.38</v>
+      </c>
+      <c r="K9" t="n">
+        <v>594.9299999999999</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="n">
-        <v>45613</v>
+        <v>46010</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>89721.97</v>
+        <v>88179.07000000001</v>
       </c>
       <c r="D10" t="n">
-        <v>93294.83</v>
+        <v>86901.13</v>
       </c>
       <c r="E10" t="n">
-        <v>93305.83</v>
+        <v>93279.86</v>
       </c>
       <c r="F10" s="1" t="n">
-        <v>45616</v>
+        <v>46027</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I10" t="n">
-        <v>-215.45</v>
+        <v>25.56</v>
       </c>
       <c r="J10" t="n">
-        <v>475.76</v>
+        <v>101.88</v>
+      </c>
+      <c r="K10" t="n">
+        <v>696.8099999999999</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
-        <v>45618</v>
+        <v>46029</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
@@ -2390,71 +7207,77 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>98927.35000000001</v>
+        <v>91197.96000000001</v>
       </c>
       <c r="D11" t="n">
-        <v>102499.3</v>
+        <v>91969.16</v>
       </c>
       <c r="E11" t="n">
-        <v>102510.3</v>
+        <v>91202.96000000001</v>
       </c>
       <c r="F11" s="1" t="n">
-        <v>45641</v>
+        <v>46035</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H11" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I11" t="n">
-        <v>-215.4</v>
+        <v>30.85</v>
       </c>
       <c r="J11" t="n">
-        <v>260.36</v>
+        <v>-0.48</v>
+      </c>
+      <c r="K11" t="n">
+        <v>696.33</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
-        <v>45643</v>
+        <v>46043</v>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>106104.91</v>
+        <v>89610.36</v>
       </c>
       <c r="D12" t="n">
-        <v>108723.05</v>
+        <v>88280.83</v>
       </c>
       <c r="E12" t="n">
-        <v>100879.63</v>
+        <v>88269.83</v>
       </c>
       <c r="F12" s="1" t="n">
-        <v>45644</v>
+        <v>46047</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H12" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I12" t="n">
-        <v>313.1</v>
+        <v>26.59</v>
       </c>
       <c r="J12" t="n">
-        <v>573.46</v>
+        <v>-26.95</v>
+      </c>
+      <c r="K12" t="n">
+        <v>669.38</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="n">
-        <v>45657</v>
+        <v>46052</v>
       </c>
       <c r="B13" t="inlineStr">
         <is>
@@ -2462,35 +7285,38 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>93400.73</v>
+        <v>84028.03</v>
       </c>
       <c r="D13" t="n">
-        <v>89896.53</v>
+        <v>82637.39999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>98646.03</v>
+        <v>82626.39999999999</v>
       </c>
       <c r="F13" s="1" t="n">
-        <v>45663</v>
+        <v>46053</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H13" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I13" t="n">
-        <v>314.3</v>
+        <v>27.81</v>
       </c>
       <c r="J13" t="n">
-        <v>887.76</v>
+        <v>-28.17</v>
+      </c>
+      <c r="K13" t="n">
+        <v>641.2</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="n">
-        <v>45667</v>
+        <v>46055</v>
       </c>
       <c r="B14" t="inlineStr">
         <is>
@@ -2498,52 +7324,55 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>94770.12</v>
+        <v>78727.60000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>91284.10000000001</v>
+        <v>76885.21000000001</v>
       </c>
       <c r="E14" t="n">
-        <v>99988.14999999999</v>
+        <v>76874.21000000001</v>
       </c>
       <c r="F14" s="1" t="n">
-        <v>45672</v>
+        <v>46056</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I14" t="n">
-        <v>312.66</v>
+        <v>18.42</v>
       </c>
       <c r="J14" t="n">
-        <v>1200.42</v>
+        <v>-18.6</v>
+      </c>
+      <c r="K14" t="n">
+        <v>622.6</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
-        <v>45675</v>
+        <v>46058</v>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SELL</t>
+          <t>BUY</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>104387.16</v>
+        <v>63505.69</v>
       </c>
       <c r="D15" t="n">
-        <v>108250.4</v>
+        <v>61660.49</v>
       </c>
       <c r="E15" t="n">
-        <v>98603.28999999999</v>
+        <v>69030.3</v>
       </c>
       <c r="F15" s="1" t="n">
-        <v>45690</v>
+        <v>46059</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -2551,18 +7380,21 @@
         </is>
       </c>
       <c r="H15" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I15" t="n">
-        <v>346.61</v>
+        <v>18.45</v>
       </c>
       <c r="J15" t="n">
-        <v>1547.03</v>
+        <v>55.18</v>
+      </c>
+      <c r="K15" t="n">
+        <v>677.77</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="n">
-        <v>45714</v>
+        <v>46061</v>
       </c>
       <c r="B16" t="inlineStr">
         <is>
@@ -2570,35 +7402,38 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>83998.89999999999</v>
+        <v>70533.59</v>
       </c>
       <c r="D16" t="n">
-        <v>81851.34</v>
+        <v>67421.78</v>
       </c>
       <c r="E16" t="n">
-        <v>86851.3</v>
+        <v>67410.78</v>
       </c>
       <c r="F16" s="1" t="n">
-        <v>45718</v>
+        <v>46064</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>TP</t>
+          <t>SL</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
       <c r="I16" t="n">
-        <v>170.72</v>
+        <v>31.12</v>
       </c>
       <c r="J16" t="n">
-        <v>1717.76</v>
+        <v>-31.3</v>
+      </c>
+      <c r="K16" t="n">
+        <v>646.48</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="n">
-        <v>45726</v>
+        <v>46077</v>
       </c>
       <c r="B17" t="inlineStr">
         <is>
@@ -2606,16 +7441,16 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>79016.96000000001</v>
+        <v>64134.75</v>
       </c>
       <c r="D17" t="n">
-        <v>74142.57000000001</v>
+        <v>62976.03</v>
       </c>
       <c r="E17" t="n">
-        <v>85505.14999999999</v>
+        <v>67599.92</v>
       </c>
       <c r="F17" s="1" t="n">
-        <v>45735</v>
+        <v>46078</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -2623,54 +7458,60 @@
         </is>
       </c>
       <c r="H17" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I17" t="n">
-        <v>388.87</v>
+        <v>23.17</v>
       </c>
       <c r="J17" t="n">
-        <v>2106.63</v>
+        <v>69.16</v>
+      </c>
+      <c r="K17" t="n">
+        <v>715.64</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="n">
-        <v>45754</v>
+        <v>46086</v>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>BUY</t>
+          <t>SELL</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>79432.8</v>
+        <v>70976.42999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>77253.24000000001</v>
+        <v>72539.03</v>
       </c>
       <c r="E18" t="n">
-        <v>77242.24000000001</v>
+        <v>66299.61</v>
       </c>
       <c r="F18" s="1" t="n">
-        <v>45755</v>
+        <v>46089</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TP</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I18" t="n">
-        <v>-131.85</v>
+        <v>31.25</v>
       </c>
       <c r="J18" t="n">
-        <v>1974.77</v>
+        <v>93.40000000000001</v>
+      </c>
+      <c r="K18" t="n">
+        <v>809.04</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="n">
-        <v>45774</v>
+        <v>46148</v>
       </c>
       <c r="B19" t="inlineStr">
         <is>
@@ -2678,930 +7519,33 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>93801.88</v>
+        <v>81353.62</v>
       </c>
       <c r="D19" t="n">
-        <v>95502.50999999999</v>
+        <v>82224.37</v>
       </c>
       <c r="E19" t="n">
-        <v>95513.50999999999</v>
+        <v>80870.75</v>
       </c>
       <c r="F19" s="1" t="n">
-        <v>45778</v>
+        <v>46152</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>SL</t>
+          <t>TRAIL</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="I19" t="n">
-        <v>-103.12</v>
+        <v>34.83</v>
       </c>
       <c r="J19" t="n">
-        <v>1871.66</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="n">
-        <v>45786</v>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
-        <v>102929.8</v>
-      </c>
-      <c r="D20" t="n">
-        <v>104857.49</v>
-      </c>
-      <c r="E20" t="n">
-        <v>104868.49</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>45795</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H20" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I20" t="n">
-        <v>-116.74</v>
-      </c>
-      <c r="J20" t="n">
-        <v>1754.91</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="n">
-        <v>45799</v>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>111466.01</v>
-      </c>
-      <c r="D21" t="n">
-        <v>113517.65</v>
-      </c>
-      <c r="E21" t="n">
-        <v>108741.5</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>45800</v>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H21" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I21" t="n">
-        <v>163.05</v>
-      </c>
-      <c r="J21" t="n">
-        <v>1917.97</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="n">
-        <v>45814</v>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>104432.05</v>
-      </c>
-      <c r="D22" t="n">
-        <v>102524.39</v>
-      </c>
-      <c r="E22" t="n">
-        <v>106964.6</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>45817</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H22" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I22" t="n">
-        <v>151.53</v>
-      </c>
-      <c r="J22" t="n">
-        <v>2069.5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="n">
-        <v>45830</v>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>100910.23</v>
-      </c>
-      <c r="D23" t="n">
-        <v>99074.00999999999</v>
-      </c>
-      <c r="E23" t="n">
-        <v>103347.54</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>45831</v>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H23" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I23" t="n">
-        <v>145.82</v>
-      </c>
-      <c r="J23" t="n">
-        <v>2215.32</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="n">
-        <v>45842</v>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>108070.4</v>
-      </c>
-      <c r="D24" t="n">
-        <v>110075.79</v>
-      </c>
-      <c r="E24" t="n">
-        <v>110086.79</v>
-      </c>
-      <c r="F24" s="1" t="n">
-        <v>45847</v>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H24" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I24" t="n">
-        <v>-121.4</v>
-      </c>
-      <c r="J24" t="n">
-        <v>2093.91</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="n">
-        <v>45849</v>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C25" t="n">
-        <v>117607.61</v>
-      </c>
-      <c r="D25" t="n">
-        <v>119687.56</v>
-      </c>
-      <c r="E25" t="n">
-        <v>119698.56</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>45852</v>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H25" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I25" t="n">
-        <v>-125.88</v>
-      </c>
-      <c r="J25" t="n">
-        <v>1968.04</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="n">
-        <v>45854</v>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C26" t="n">
-        <v>118719.19</v>
-      </c>
-      <c r="D26" t="n">
-        <v>121065.63</v>
-      </c>
-      <c r="E26" t="n">
-        <v>114037.3</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>45870</v>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H26" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I26" t="n">
-        <v>280.49</v>
-      </c>
-      <c r="J26" t="n">
-        <v>2248.53</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="n">
-        <v>45883</v>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C27" t="n">
-        <v>118499.27</v>
-      </c>
-      <c r="D27" t="n">
-        <v>120751.62</v>
-      </c>
-      <c r="E27" t="n">
-        <v>114005.57</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>45888</v>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H27" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I27" t="n">
-        <v>269.2</v>
-      </c>
-      <c r="J27" t="n">
-        <v>2517.73</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="n">
-        <v>45895</v>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C28" t="n">
-        <v>111906.3</v>
-      </c>
-      <c r="D28" t="n">
-        <v>107574.09</v>
-      </c>
-      <c r="E28" t="n">
-        <v>118393.61</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>45932</v>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I28" t="n">
-        <v>388.82</v>
-      </c>
-      <c r="J28" t="n">
-        <v>2906.55</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="n">
-        <v>45934</v>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C29" t="n">
-        <v>122368.74</v>
-      </c>
-      <c r="D29" t="n">
-        <v>125688.94</v>
-      </c>
-      <c r="E29" t="n">
-        <v>117399.45</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>45940</v>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H29" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I29" t="n">
-        <v>297.74</v>
-      </c>
-      <c r="J29" t="n">
-        <v>3204.29</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="n">
-        <v>45966</v>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C30" t="n">
-        <v>103926.88</v>
-      </c>
-      <c r="D30" t="n">
-        <v>101155.26</v>
-      </c>
-      <c r="E30" t="n">
-        <v>101144.26</v>
-      </c>
-      <c r="F30" s="1" t="n">
-        <v>45974</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H30" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I30" t="n">
-        <v>-167.38</v>
-      </c>
-      <c r="J30" t="n">
-        <v>3036.91</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="n">
-        <v>45976</v>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C31" t="n">
-        <v>95552.32000000001</v>
-      </c>
-      <c r="D31" t="n">
-        <v>91939.17999999999</v>
-      </c>
-      <c r="E31" t="n">
-        <v>91928.17999999999</v>
-      </c>
-      <c r="F31" s="1" t="n">
-        <v>45978</v>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H31" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I31" t="n">
-        <v>-217.87</v>
-      </c>
-      <c r="J31" t="n">
-        <v>2819.04</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="n">
-        <v>45980</v>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C32" t="n">
-        <v>91331.48</v>
-      </c>
-      <c r="D32" t="n">
-        <v>88177</v>
-      </c>
-      <c r="E32" t="n">
-        <v>88166</v>
-      </c>
-      <c r="F32" s="1" t="n">
-        <v>45981</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H32" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I32" t="n">
-        <v>-190.35</v>
-      </c>
-      <c r="J32" t="n">
-        <v>2628.69</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="n">
-        <v>45983</v>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C33" t="n">
-        <v>84786</v>
-      </c>
-      <c r="D33" t="n">
-        <v>81582.13</v>
-      </c>
-      <c r="E33" t="n">
-        <v>91182.75</v>
-      </c>
-      <c r="F33" s="1" t="n">
-        <v>45988</v>
-      </c>
-      <c r="G33" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H33" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I33" t="n">
-        <v>383.38</v>
-      </c>
-      <c r="J33" t="n">
-        <v>3012.08</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="n">
-        <v>46025</v>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C34" t="n">
-        <v>90587.13</v>
-      </c>
-      <c r="D34" t="n">
-        <v>91438.60000000001</v>
-      </c>
-      <c r="E34" t="n">
-        <v>91449.60000000001</v>
-      </c>
-      <c r="F34" s="1" t="n">
-        <v>46027</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H34" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I34" t="n">
-        <v>-52.17</v>
-      </c>
-      <c r="J34" t="n">
-        <v>2959.91</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="n">
-        <v>46029</v>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C35" t="n">
-        <v>91197.96000000001</v>
-      </c>
-      <c r="D35" t="n">
-        <v>92354.77</v>
-      </c>
-      <c r="E35" t="n">
-        <v>92365.77</v>
-      </c>
-      <c r="F35" s="1" t="n">
-        <v>46035</v>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H35" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I35" t="n">
-        <v>-70.48999999999999</v>
-      </c>
-      <c r="J35" t="n">
-        <v>2889.42</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="n">
-        <v>46037</v>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C36" t="n">
-        <v>95535.14</v>
-      </c>
-      <c r="D36" t="n">
-        <v>97314.99000000001</v>
-      </c>
-      <c r="E36" t="n">
-        <v>91986.45</v>
-      </c>
-      <c r="F36" s="1" t="n">
-        <v>46042</v>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H36" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I36" t="n">
-        <v>212.5</v>
-      </c>
-      <c r="J36" t="n">
-        <v>3101.92</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="n">
-        <v>46048</v>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C37" t="n">
-        <v>88348.45</v>
-      </c>
-      <c r="D37" t="n">
-        <v>86233.58</v>
-      </c>
-      <c r="E37" t="n">
-        <v>86222.58</v>
-      </c>
-      <c r="F37" s="1" t="n">
-        <v>46051</v>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H37" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I37" t="n">
-        <v>-127.97</v>
-      </c>
-      <c r="J37" t="n">
-        <v>2973.95</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="n">
-        <v>46053</v>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C38" t="n">
-        <v>78713.39</v>
-      </c>
-      <c r="D38" t="n">
-        <v>76579.61</v>
-      </c>
-      <c r="E38" t="n">
-        <v>76568.61</v>
-      </c>
-      <c r="F38" s="1" t="n">
-        <v>46056</v>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H38" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I38" t="n">
-        <v>-129.11</v>
-      </c>
-      <c r="J38" t="n">
-        <v>2844.84</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="n">
-        <v>46058</v>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C39" t="n">
-        <v>63505.69</v>
-      </c>
-      <c r="D39" t="n">
-        <v>60737.89</v>
-      </c>
-      <c r="E39" t="n">
-        <v>69030.3</v>
-      </c>
-      <c r="F39" s="1" t="n">
-        <v>46059</v>
-      </c>
-      <c r="G39" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H39" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I39" t="n">
-        <v>331.06</v>
-      </c>
-      <c r="J39" t="n">
-        <v>3175.9</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="n">
-        <v>46077</v>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C40" t="n">
-        <v>64134.75</v>
-      </c>
-      <c r="D40" t="n">
-        <v>61817.3</v>
-      </c>
-      <c r="E40" t="n">
-        <v>67599.92</v>
-      </c>
-      <c r="F40" s="1" t="n">
-        <v>46078</v>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H40" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I40" t="n">
-        <v>207.49</v>
-      </c>
-      <c r="J40" t="n">
-        <v>3383.39</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="n">
-        <v>46086</v>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C41" t="n">
-        <v>70976.42999999999</v>
-      </c>
-      <c r="D41" t="n">
-        <v>74101.64</v>
-      </c>
-      <c r="E41" t="n">
-        <v>66299.61</v>
-      </c>
-      <c r="F41" s="1" t="n">
-        <v>46089</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H41" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I41" t="n">
-        <v>280.19</v>
-      </c>
-      <c r="J41" t="n">
-        <v>3663.58</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="n">
-        <v>46097</v>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C42" t="n">
-        <v>74712.96000000001</v>
-      </c>
-      <c r="D42" t="n">
-        <v>77697.39</v>
-      </c>
-      <c r="E42" t="n">
-        <v>70247.3</v>
-      </c>
-      <c r="F42" s="1" t="n">
-        <v>46100</v>
-      </c>
-      <c r="G42" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H42" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I42" t="n">
-        <v>267.52</v>
-      </c>
-      <c r="J42" t="n">
-        <v>3931.1</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="1" t="n">
-        <v>46109</v>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>BUY</t>
-        </is>
-      </c>
-      <c r="C43" t="n">
-        <v>66362.07000000001</v>
-      </c>
-      <c r="D43" t="n">
-        <v>63478.44</v>
-      </c>
-      <c r="E43" t="n">
-        <v>70676.52</v>
-      </c>
-      <c r="F43" s="1" t="n">
-        <v>46119</v>
-      </c>
-      <c r="G43" t="inlineStr">
-        <is>
-          <t>TP</t>
-        </is>
-      </c>
-      <c r="H43" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I43" t="n">
-        <v>258.45</v>
-      </c>
-      <c r="J43" t="n">
-        <v>4189.55</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="1" t="n">
-        <v>46122</v>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>SELL</t>
-        </is>
-      </c>
-      <c r="C44" t="n">
-        <v>72934.07000000001</v>
-      </c>
-      <c r="D44" t="n">
-        <v>74905.52</v>
-      </c>
-      <c r="E44" t="n">
-        <v>74916.52</v>
-      </c>
-      <c r="F44" s="1" t="n">
-        <v>46128</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>SL</t>
-        </is>
-      </c>
-      <c r="H44" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I44" t="n">
-        <v>-119.37</v>
-      </c>
-      <c r="J44" t="n">
-        <v>4070.18</v>
+        <v>19.03</v>
+      </c>
+      <c r="K19" t="n">
+        <v>828.0700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -3615,7 +7559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3651,10 +7595,20 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>be_trigger_R</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>trail_R</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>max_hold</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>is_score</t>
         </is>
@@ -3662,7 +7616,7 @@
     </row>
     <row r="2">
       <c r="A2" s="1" t="n">
-        <v>45533</v>
+        <v>45920</v>
       </c>
       <c r="B2" t="n">
         <v>20</v>
@@ -3674,21 +7628,27 @@
         <v>1.5</v>
       </c>
       <c r="E2" t="n">
+        <v>1</v>
+      </c>
+      <c r="F2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
         <v>1.5</v>
       </c>
-      <c r="F2" t="n">
-        <v>3</v>
-      </c>
-      <c r="G2" t="n">
+      <c r="I2" t="n">
         <v>48</v>
       </c>
-      <c r="H2" t="n">
-        <v>673.35</v>
+      <c r="J2" t="n">
+        <v>7583.25</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
-        <v>45593</v>
+        <v>45980</v>
       </c>
       <c r="B3" t="n">
         <v>20</v>
@@ -3700,24 +7660,30 @@
         <v>1.5</v>
       </c>
       <c r="E3" t="n">
+        <v>1</v>
+      </c>
+      <c r="F3" t="n">
+        <v>4</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
         <v>1.5</v>
       </c>
-      <c r="F3" t="n">
-        <v>3</v>
-      </c>
-      <c r="G3" t="n">
+      <c r="I3" t="n">
         <v>48</v>
       </c>
-      <c r="H3" t="n">
-        <v>901.42</v>
+      <c r="J3" t="n">
+        <v>7362.22</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
-        <v>45653</v>
+        <v>46040</v>
       </c>
       <c r="B4" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="C4" t="n">
         <v>14</v>
@@ -3726,21 +7692,27 @@
         <v>1.5</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F4" t="n">
         <v>3</v>
       </c>
       <c r="G4" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="I4" t="n">
         <v>48</v>
       </c>
-      <c r="H4" t="n">
-        <v>289.26</v>
+      <c r="J4" t="n">
+        <v>2226.62</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n">
-        <v>45713</v>
+        <v>46100</v>
       </c>
       <c r="B5" t="n">
         <v>20</v>
@@ -3749,175 +7721,25 @@
         <v>14</v>
       </c>
       <c r="D5" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="E5" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="n">
+        <v>1</v>
+      </c>
+      <c r="I5" t="n">
         <v>48</v>
       </c>
-      <c r="H5" t="n">
-        <v>89.14</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="n">
-        <v>45773</v>
-      </c>
-      <c r="B6" t="n">
-        <v>20</v>
-      </c>
-      <c r="C6" t="n">
-        <v>14</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F6" t="n">
-        <v>2</v>
-      </c>
-      <c r="G6" t="n">
-        <v>48</v>
-      </c>
-      <c r="H6" t="n">
-        <v>488.28</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n">
-        <v>45833</v>
-      </c>
-      <c r="B7" t="n">
-        <v>40</v>
-      </c>
-      <c r="C7" t="n">
-        <v>14</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F7" t="n">
-        <v>3</v>
-      </c>
-      <c r="G7" t="n">
-        <v>48</v>
-      </c>
-      <c r="H7" t="n">
-        <v>384.33</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="n">
-        <v>45893</v>
-      </c>
-      <c r="B8" t="n">
-        <v>20</v>
-      </c>
-      <c r="C8" t="n">
-        <v>14</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E8" t="n">
-        <v>2</v>
-      </c>
-      <c r="F8" t="n">
-        <v>3</v>
-      </c>
-      <c r="G8" t="n">
-        <v>48</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1237.08</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="n">
-        <v>45953</v>
-      </c>
-      <c r="B9" t="n">
-        <v>20</v>
-      </c>
-      <c r="C9" t="n">
-        <v>14</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F9" t="n">
-        <v>3</v>
-      </c>
-      <c r="G9" t="n">
-        <v>48</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1046.52</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="n">
-        <v>46013</v>
-      </c>
-      <c r="B10" t="n">
-        <v>20</v>
-      </c>
-      <c r="C10" t="n">
-        <v>14</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="F10" t="n">
-        <v>3</v>
-      </c>
-      <c r="G10" t="n">
-        <v>48</v>
-      </c>
-      <c r="H10" t="n">
-        <v>715.47</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="n">
-        <v>46073</v>
-      </c>
-      <c r="B11" t="n">
-        <v>20</v>
-      </c>
-      <c r="C11" t="n">
-        <v>14</v>
-      </c>
-      <c r="D11" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="E11" t="n">
-        <v>2</v>
-      </c>
-      <c r="F11" t="n">
-        <v>3</v>
-      </c>
-      <c r="G11" t="n">
-        <v>48</v>
-      </c>
-      <c r="H11" t="n">
-        <v>491.66</v>
+      <c r="J5" t="n">
+        <v>5635.22</v>
       </c>
     </row>
   </sheetData>
